--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Exercises" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$L$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$L$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTA(Exercises!$A$2:$A$72)</f>
+        <f>COUNTA(Exercises!$A$2:$A$75)</f>
         <v/>
       </c>
     </row>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>COUNTIF(Exercises!$K$2:$K$72,"Approve")</f>
+        <f>COUNTIF(Exercises!$K$2:$K$75,"Approve")</f>
         <v/>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTIF(Exercises!$K$2:$K$72,"Fix")</f>
+        <f>COUNTIF(Exercises!$K$2:$K$75,"Fix")</f>
         <v/>
       </c>
     </row>
@@ -795,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1895,175 +1895,338 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>neutral_grip_floor_press</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Neutral-grip floor press</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Mid chest (Pectoralis major · sternal head): primary, 0.9
+Triceps (Triceps brachii): secondary, 0.6
+Front shoulders (Deltoid · front head): secondary, 0.2</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbells</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Elbow / wrist</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Lie on the floor, palms facing each other; lower until your upper arms touch the floor, then press up.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Main work</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>neutral_grip_machine_chest_press</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Neutral-grip machine chest press</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Mid chest (Pectoralis major · sternal head): primary, 1.0
+Triceps (Triceps brachii): secondary, 0.5
+Front shoulders (Deltoid · front head): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Machine</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Palms facing in, handles at mid-chest; press out without locking your elbows, stop before your hands pass your chest on the way back.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Main work</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>short_range_incline_push_up</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Short-range incline push-up</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Mid chest (Pectoralis major · sternal head): primary, 0.8
+Lower chest (Pectoralis major · lower fibers): secondary, 0.4
+Triceps (Triceps brachii): secondary, 0.4
+Front shoulders (Deltoid · front head): secondary, 0.2</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Bench</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Elbow / wrist</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Hands on a bench, body straight; lower only halfway, then push back up.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Main work</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>dumbbell_shoulder_press</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Dumbbell shoulder press</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Front shoulders (Deltoid · front head): primary, 1.0
 Triceps (Triceps brachii): secondary, 0.5
 Traps (Trapezius): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Shoulder, Neck</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Press the dumbbells overhead without arching your back.</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>band_front_raise</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Band front raise</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Front shoulders (Deltoid · front head): primary, 0.9</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Shoulder</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Raise straight arms to shoulder height and lower slowly.</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>band_face_pull</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Band face pull</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Rear shoulders (Deltoid · rear head): primary, 1.0
 Upper back (Rhomboids and middle trapezius): secondary, 0.6
 Traps (Trapezius): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pull the band toward your face, elbows high and out.</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>one_arm_dumbbell_row</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>One-arm dumbbell row</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Upper back (Rhomboids and middle trapezius): primary, 0.9
 Lats (Latissimus dorsi): primary, 0.8
@@ -2071,692 +2234,692 @@
 Rear shoulders (Deltoid · rear head): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Dumbbells, Bench</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Hand on the bench; pull the dumbbell to your hip.</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>band_row</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Band row</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Upper back (Rhomboids and middle trapezius): primary, 1.0
 Lats (Latissimus dorsi): secondary, 0.5
 Biceps (Biceps brachii): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="E28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pull the band to your ribs, squeezing your shoulder blades.</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>lat_pulldown</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Lat pulldown</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Lats (Latissimus dorsi): primary, 1.0
 Biceps (Biceps brachii): secondary, 0.5
 Upper back (Rhomboids and middle trapezius): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Cable</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Shoulder</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Pull the bar to your upper chest, chest up.</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>seated_cable_row</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Seated cable row</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Upper back (Rhomboids and middle trapezius): primary, 1.0
 Lats (Latissimus dorsi): secondary, 0.6
 Biceps (Biceps brachii): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Cable</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Sit tall and pull the handle to your belly.</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>dumbbell_shrug</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Dumbbell shrug</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Traps (Trapezius): primary, 1.0
 Forearms (Wrist flexors and extensors): stabilizer, 0.3</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Neck</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Lift your shoulders toward your ears, pause, lower.</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>superman</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Superman</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Lower back (Erector spinae): primary, 1.0
 Glutes (Gluteus maximus and medius): secondary, 0.5</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="E32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Lower back, Pregnant / postpartum, Recent surgery</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Lying face down, lift arms and legs a little, then lower.</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>bird_dog</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Bird dog</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Lower back (Erector spinae): primary, 0.8
 Glutes (Gluteus maximus and medius): secondary, 0.5
 Lower abs (Rectus abdominis · lower): stabilizer, 0.4</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="E33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Recent surgery</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>On hands and knees, reach one arm and the opposite leg long.</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>dumbbell_curl</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Dumbbell curl</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Biceps (Biceps brachii): primary, 1.0
 Forearms (Wrist flexors and extensors): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Elbow / wrist</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Elbows by your sides; curl up and lower slowly.</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>band_curl</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Band curl</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Biceps (Biceps brachii): primary, 0.9
 Forearms (Wrist flexors and extensors): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="E35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Elbow / wrist</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Stand on the band and curl your hands to your shoulders.</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>overhead_dumbbell_triceps_extension</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Overhead triceps extension</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Triceps (Triceps brachii): primary, 1.0</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E36" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Shoulder, Elbow / wrist</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Hold a dumbbell overhead; lower behind your head and extend.</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>bench_dip</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Bench dip</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Triceps (Triceps brachii): primary, 1.0
 Lower chest (Pectoralis major · lower fibers): secondary, 0.4
 Front shoulders (Deltoid · front head): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Bench</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E37" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Shoulder, Elbow / wrist</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Hands on the bench behind you; bend your elbows and press up.</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>band_triceps_pushdown</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Band triceps pushdown</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Triceps (Triceps brachii): primary, 0.9</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="E38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Elbow / wrist</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Elbows fixed at your sides; push the band down.</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>dumbbell_wrist_curl</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Dumbbell wrist curl</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Forearms (Wrist flexors and extensors): primary, 1.0</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Elbow / wrist</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>Forearms on your thighs; curl the dumbbells with your wrists.</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>plank</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Plank</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Upper abs (Rectus abdominis · upper): primary, 0.7
 Lower abs (Rectus abdominis · lower): primary, 0.7
@@ -2764,1172 +2927,1172 @@
 Front shoulders (Deltoid · front head): stabilizer, 0.3</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E40" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Shoulder, Recent surgery, High blood pressure</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>Elbows under shoulders, body in a straight line. Breathe.</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>dead_bug</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Dead bug</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Lower abs (Rectus abdominis · lower): primary, 1.0
 Upper abs (Rectus abdominis · upper): secondary, 0.5</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Pregnant / postpartum, Recent surgery</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>On your back, lower the opposite arm and leg, low back down.</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>crunch</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Crunch</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Upper abs (Rectus abdominis · upper): primary, 1.0
 Lower abs (Rectus abdominis · lower): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="E42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Neck, Pregnant / postpartum, Recent surgery, Osteoporosis</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Knees bent; curl your shoulders off the floor, then lower.</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>reverse_crunch</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Reverse crunch</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Lower abs (Rectus abdominis · lower): primary, 1.0
 Upper abs (Rectus abdominis · upper): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E43" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Lower back, Pregnant / postpartum, Recent surgery</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>On your back, curl your knees toward your chest.</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K40" s="6" t="n"/>
-      <c r="L40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>side_plank</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Side plank</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Obliques (External and internal obliques): primary, 1.0
 Lower abs (Rectus abdominis · lower): secondary, 0.3
 Hips (Hip flexors): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E44" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Shoulder, Recent surgery</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>On one elbow, lift your hips into a straight line.</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>band_pallof_press</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Band Pallof press</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Obliques (External and internal obliques): primary, 1.0
 Lower abs (Rectus abdominis · lower): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="E45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Band at your side; press it straight out and resist the twist.</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>bodyweight_squat</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Bodyweight squat</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 1.0
 Glutes (Gluteus maximus and medius): secondary, 0.7
 Inner thighs (Hip adductors): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Sit back and down, knees over toes, then stand.</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>goblet_squat</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Goblet squat</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 1.0
 Glutes (Gluteus maximus and medius): secondary, 0.7
 Upper abs (Rectus abdominis · upper): stabilizer, 0.3</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E47" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Knee, Lower back</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Hold a dumbbell at your chest; squat down and stand tall.</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>sit_to_stand</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Sit to stand</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 0.9
 Glutes (Gluteus maximus and medius): secondary, 0.7</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="E48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>From a chair, stand up without using your hands, then sit slowly.</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K45" s="6" t="n"/>
-      <c r="L45" s="6" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>reverse_lunge</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Reverse lunge</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 0.8
 Glutes (Gluteus maximus and medius): primary, 0.8
 Inner thighs (Hip adductors): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E49" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Knee, Hip, Ankle / foot, Fell in the last year</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>Step back and lower both knees, then return.</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>leg_press</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Leg press</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 1.0
 Glutes (Gluteus maximus and medius): secondary, 0.6</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Machine</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Knee, Lower back</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>Feet hip-width; lower with control and press away.</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K47" s="6" t="n"/>
-      <c r="L47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>glute_bridge</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Glute bridge</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Glutes (Gluteus maximus and medius): primary, 1.0
 Hamstrings (Hamstrings): secondary, 0.5
 Lower back (Erector spinae): stabilizer, 0.2</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Pregnant / postpartum</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>On your back, drive through your heels and lift your hips.</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>dumbbell_romanian_deadlift</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Dumbbell Romanian deadlift</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Hamstrings (Hamstrings): primary, 1.0
 Glutes (Gluteus maximus and medius): primary, 0.8
 Lower back (Erector spinae): secondary, 0.5</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Dumbbells</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E52" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Lower back, Recent surgery</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Soft knees; hinge at the hips, dumbbells close to your legs.</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>lying_hamstring_curl_machine</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Lying hamstring curl</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Hamstrings (Hamstrings): primary, 1.0
 Calves (Gastrocnemius and soleus): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Machine</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>13+ (teens)</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Curl your heels toward your glutes and lower slowly.</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>standing_calf_raise</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Standing calf raise</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Calves (Gastrocnemius and soleus): primary, 1.0</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="E54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Ankle / foot</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Rise onto your toes, pause, lower slowly.</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>seated_knee_raise</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Seated knee raise</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Hips (Hip flexors): primary, 1.0
 Lower abs (Rectus abdominis · lower): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Hip</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Sit tall and lift one knee toward your chest.</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>side_lying_adductor_raise</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>Side-lying inner thigh raise</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Inner thighs (Hip adductors): primary, 1.0</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="E56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Hip</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>Lying on your side, lift the bottom leg a little.</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>wall_tibialis_raise</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Wall tibialis raise</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Shins (Tibialis anterior): primary, 1.0</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="E57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>Ankle / foot</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>Back on a wall, lift your toes up and lower.</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>band_terminal_knee_extension</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Band knee extension</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Knees (Muscles around the knee): primary, 0.8
 Quads (Quadriceps): primary, 0.7</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="E58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>Band behind your knee; straighten the knee against it.</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>step_up</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Step-up</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 0.9
 Glutes (Gluteus maximus and medius): primary, 0.7</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Bench</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Knee, Ankle / foot, Fell in the last year</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>Step onto the bench, stand tall, step down with control.</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Main work, Finisher: cardio</t>
         </is>
       </c>
-      <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>single_leg_balance</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Single-leg balance</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Calves (Gastrocnemius and soleus): primary, 0.6
 Glutes (Gluteus maximus and medius): secondary, 0.5
 Shins (Tibialis anterior): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="E60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>Stand on one leg; hold a support if you need it.</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>Main work, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K57" s="6" t="n"/>
-      <c r="L57" s="6" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="K60" s="6" t="n"/>
+      <c r="L60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>mountain_climber</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Mountain climber</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Lower abs (Rectus abdominis · lower): primary, 0.6
 Hips (Hip flexors): secondary, 0.5
 Front shoulders (Deltoid · front head): stabilizer, 0.4</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E61" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Shoulder, Elbow / wrist, Heart condition, Pregnant / postpartum, Recent surgery, High blood pressure</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>In a plank, drive your knees in, one after the other.</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>Finisher: cardio</t>
         </is>
       </c>
-      <c r="K58" s="6" t="n"/>
-      <c r="L58" s="6" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="K61" s="6" t="n"/>
+      <c r="L61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>doorway_chest_stretch</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Doorway chest stretch</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Mid chest (Pectoralis major · sternal head): primary, 0.8
 Upper chest (Pectoralis major · clavicular head): secondary, 0.6
@@ -3937,735 +4100,735 @@
 Front shoulders (Deltoid · front head): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="E62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>Shoulder</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>Forearm on a door frame; lean forward gently.</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K59" s="6" t="n"/>
-      <c r="L59" s="6" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="K62" s="6" t="n"/>
+      <c r="L62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>cross_body_shoulder_stretch</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Cross-body shoulder stretch</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Rear shoulders (Deltoid · rear head): primary, 0.8
 Front shoulders (Deltoid · front head): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="E63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>Pull one arm across your chest with the other.</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="K63" s="6" t="n"/>
+      <c r="L63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>overhead_triceps_stretch</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Overhead triceps stretch</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Triceps (Triceps brachii): primary, 0.8
 Lats (Latissimus dorsi): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="E64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>Shoulder</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Hand behind your head; gently press the elbow.</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K61" s="6" t="n"/>
-      <c r="L61" s="6" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="K64" s="6" t="n"/>
+      <c r="L64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>standing_quad_stretch</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Standing quad stretch</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 0.9
 Hips (Hip flexors): secondary, 0.4
 Knees (Muscles around the knee): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="E65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>Hold a support; pull your heel toward your glute.</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>seated_hamstring_stretch</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Seated hamstring stretch</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Hamstrings (Hamstrings): primary, 0.9
 Calves (Gastrocnemius and soleus): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="E66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>Leg straight; lean forward from the hips.</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="6" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>seated_figure_four_stretch</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Seated figure-four stretch</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Glutes (Gluteus maximus and medius): primary, 0.9
 Hips (Hip flexors): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="E67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>Hip, Knee</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>Ankle over the other knee; lean forward gently.</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>wall_calf_stretch</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Wall calf stretch</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Calves (Gastrocnemius and soleus): primary, 0.9
 Shins (Tibialis anterior): secondary, 0.3</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="E68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>Ankle / foot</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>Hands on a wall, back leg straight, heel down.</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K65" s="6" t="n"/>
-      <c r="L65" s="6" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>childs_pose</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Child's pose</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Lats (Latissimus dorsi): primary, 0.7
 Lower back (Erector spinae): primary, 0.6
 Upper back (Rhomboids and middle trapezius): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="E69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>Sit back on your heels and reach your arms forward.</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="K69" s="6" t="n"/>
+      <c r="L69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>kneeling_hip_flexor_stretch</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Kneeling hip flexor stretch</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Hips (Hip flexors): primary, 0.9
 Quads (Quadriceps): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="E70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>One knee down; shift your hips forward gently.</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K67" s="6" t="n"/>
-      <c r="L67" s="6" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="K70" s="6" t="n"/>
+      <c r="L70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>upper_trap_stretch</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Upper trap stretch</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Traps (Trapezius): primary, 0.8</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="E71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>Neck</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>Tilt your ear toward your shoulder; relax.</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="6" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="K71" s="6" t="n"/>
+      <c r="L71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>standing_side_stretch</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Side stretch</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Obliques (External and internal obliques): primary, 0.8
 Lats (Latissimus dorsi): secondary, 0.5</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="E72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>Reach one arm overhead and lean to the side.</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>hug_upper_back_stretch</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Upper back hug stretch</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Upper back (Rhomboids and middle trapezius): primary, 0.8
 Rear shoulders (Deltoid · rear head): secondary, 0.4</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="E73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Hug yourself and round your upper back.</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K70" s="6" t="n"/>
-      <c r="L70" s="6" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>biceps_wall_stretch</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Biceps wall stretch</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Biceps (Biceps brachii): primary, 0.8
 Forearms (Wrist flexors and extensors): secondary, 0.5</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="E74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>Shoulder</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>Palm on a wall behind you; turn away slowly.</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>box_breathing</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Slow breathing</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>— (breathing, no muscle mapping)</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="E75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Standing, With support, Seated</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>Breathe in for 4, hold 4, out for 4, hold 4.</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Cool-down: breathing</t>
         </is>
       </c>
-      <c r="K72" s="6" t="n"/>
-      <c r="L72" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L72"/>
+  <autoFilter ref="A1:L75"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
+    <dataValidation sqref="K2:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Exercises" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Repair tests" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$L$75</definedName>
@@ -204,7 +205,7 @@
     <author>TapStrong</author>
   </authors>
   <commentList>
-    <comment ref="A24" authorId="0" shapeId="0">
+    <comment ref="A26" authorId="0" shapeId="0">
       <text>
         <t>Stored with each certified review (name + credential, e.g. NSCA-CSCS).</t>
       </text>
@@ -502,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -568,219 +569,237 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>4. Repair tests (tab "Repair tests"): are the protocol, the "good" target per age mode, the contraindications and the muscles each weak result sends to the 6-week plan right?</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>How to fill it in</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Only the two yellow columns on the "Exercises" tab: "Approve / Fix" (pick from the list) and "Comment". For "Fix", say what to change in the comment. Leave every other cell as it is.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Example (not part of the library):</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ID (slug)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Exercise</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Muscles (role, emphasis 0–1)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Level (1–5)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Minimum age</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Contraindications</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Cues</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Used as</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Approve / Fix (Aprovado/Corrigir)</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Comment (Comentário)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>example_squat</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Example squat</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 1.0
 Glutes (Gluteus maximus and medius): secondary, 0.7</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>9+ (kids)</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Sit back and down, knees over toes, then stand.</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>Add adductors as secondary, 0.3. Cue: keep heels down.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Progress (updates as you fill in the Exercises tab)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Exercises</t>
         </is>
       </c>
-      <c r="B18" s="7">
+      <c r="B19" s="7">
         <f>COUNTA(Exercises!$A$2:$A$75)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="B19" s="7">
+      <c r="B20" s="7">
         <f>COUNTIF(Exercises!$K$2:$K$75,"Approve")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>To fix</t>
         </is>
       </c>
-      <c r="B20" s="7">
+      <c r="B21" s="7">
         <f>COUNTIF(Exercises!$K$2:$K$75,"Fix")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Not reviewed yet</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>B18-B19-B20</f>
+      <c r="B22" s="7">
+        <f>B19-B20-B21</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Repair tests approved</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>COUNTIF('Repair tests'!$I$2:$I$6,"Approve")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Reviewer name, credential and date</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="n"/>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="K15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4834,4 +4853,307 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>How (shown to the user)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Result recorded</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Positions</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Contraindications</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>"Good" target by mode (kids / teens / adults / 60+)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Weak result → plan focus</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Approve / Fix (Aprovado/Corrigir)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Comment (Comentário)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Sit-to-stand (30 s)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Sit on a chair, arms crossed. Stand up fully and sit back down as many times as you can in 30 seconds. Count each full stand.</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Reps in 30 s</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Knee, Recent surgery</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>15 reps / 15 reps / 15 reps / 12 reps</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Strengthen: Quads, Glutes</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>single_leg_balance</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Single-leg balance</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Stand on one leg, hands on hips, eyes open. Time how long you hold before the other foot touches down. Then the other leg.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Hold time per side, seconds (max 60)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Ankle / foot, Recent surgery</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>20 s / 30 s / 30 s / 10 s</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Balance: Hips, Glutes</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>glute_bridge_hold</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Glute bridge hold</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Lie on your back, knees bent, feet flat. Lift your hips into a straight line from knees to shoulders and hold.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Hold time, seconds (max 60)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Lower back, Recent surgery</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>20 s / 30 s / 30 s / 20 s</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Strengthen: Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>front_plank</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Front plank</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Forearms and toes on the floor, body straight from head to heels. Hold without letting the hips sag.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Hold time, seconds (max 120)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder, Lower back, Pregnant / postpartum, Recent surgery</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>20 s / 30 s / 45 s / 30 s</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Strengthen: Upper abs, Lower abs, Obliques</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>shoulder_reach</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Overhead shoulder reach</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Stand with your back against a wall. Raise one straight arm overhead. Can the back of your hand touch the wall without arching your back? Then the other arm.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Reached / limited, per side</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder, Recent surgery</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Both sides reached</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Mobility: Front shoulders, Upper back</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I2:I6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Approve,Fix"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -10,9 +10,10 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Exercises" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Repair tests" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Movements" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$L$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$N$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -205,7 +206,7 @@
     <author>TapStrong</author>
   </authors>
   <commentList>
-    <comment ref="A26" authorId="0" shapeId="0">
+    <comment ref="A28" authorId="0" shapeId="0">
       <text>
         <t>Stored with each certified review (name + credential, e.g. NSCA-CSCS).</t>
       </text>
@@ -503,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -516,8 +517,10 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,230 +579,269 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5. Joint movements: does each exercise and test list every joint movement it needs, with the right range? Is a shorter range really safe where it is allowed? Tab "Movements": are the movement list, the everyday examples, the red flags and the recovery phases right?</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>How to fill it in</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Only the two yellow columns on the "Exercises" tab: "Approve / Fix" (pick from the list) and "Comment". For "Fix", say what to change in the comment. Leave every other cell as it is.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Example (not part of the library):</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ID (slug)</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Exercise</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Muscles (role, emphasis 0–1)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Level (1–5)</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Minimum age</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Contraindications</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Cues</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Used as</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Joint movements (range)</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Shorter range allowed</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Approve / Fix (Aprovado/Corrigir)</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>Comment (Comentário)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>example_squat</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Example squat</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Quads (Quadriceps): primary, 1.0
 Glutes (Gluteus maximus and medius): secondary, 0.7</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Bodyweight</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>9+ (kids)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Standing, With support</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Knee</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Sit back and down, knees over toes, then stand.</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Main work</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)
+Hip: Deep squat (full)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>Add adductors as secondary, 0.3. Cue: keep heels down.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Progress (updates as you fill in the Exercises tab)</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Exercises</t>
-        </is>
-      </c>
-      <c r="B19" s="7">
-        <f>COUNTA(Exercises!$A$2:$A$75)</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Exercises</t>
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTIF(Exercises!$K$2:$K$75,"Approve")</f>
+        <f>COUNTA(Exercises!$A$2:$A$83)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>To fix</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="B21" s="7">
-        <f>COUNTIF(Exercises!$K$2:$K$75,"Fix")</f>
+        <f>COUNTIF(Exercises!$M$2:$M$83,"Approve")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Not reviewed yet</t>
+          <t>To fix</t>
         </is>
       </c>
       <c r="B22" s="7">
-        <f>B19-B20-B21</f>
+        <f>COUNTIF(Exercises!$M$2:$M$83,"Fix")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>Not reviewed yet</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>B20-B21-B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
           <t>Repair tests approved</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>COUNTIF('Repair tests'!$I$2:$I$6,"Approve")</f>
+      <c r="B24" s="7">
+        <f>COUNTIF('Repair tests'!$J$2:$J$6,"Approve")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Movement rows approved</t>
+        </is>
+      </c>
+      <c r="B25" s="7">
+        <f>COUNTIF(Movements!$E$2:$E$200,"Approve")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Reviewer name, credential and date</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="n"/>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="K16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -814,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -827,8 +869,10 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -884,10 +928,20 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>Joint movements (range)</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Shorter range allowed</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>Approve / Fix (Aprovado/Corrigir)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Comment (Comentário)</t>
         </is>
@@ -944,8 +998,18 @@
           <t>Warm-up: easy cardio, Cool-down: walk</t>
         </is>
       </c>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="6" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (partial)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -997,8 +1061,18 @@
           <t>Warm-up: easy cardio, Cool-down: walk</t>
         </is>
       </c>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (partial)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1051,8 +1125,22 @@
           <t>Warm-up: easy cardio, Finisher: cardio</t>
         </is>
       </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side (full)
+Shoulder: Arm overhead (full)
+Hip: Leg out to the side (partial)
+Knee: Jump or run (full)
+Ankle: Jump or run (full)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1105,8 +1193,18 @@
           <t>Warm-up: easy cardio, Finisher: cardio, Cool-down: walk</t>
         </is>
       </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1159,8 +1257,19 @@
           <t>Warm-up: easy cardio, Finisher: cardio, Cool-down: walk</t>
         </is>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (partial)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1212,8 +1321,20 @@
           <t>Warm-up: mobility</t>
         </is>
       </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side (full)
+Shoulder: Raise arm in front (full)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side
+Shoulder: Raise arm in front</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1265,8 +1386,20 @@
           <t>Warm-up: mobility, Main work</t>
         </is>
       </c>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (full)
+Shoulder: Raise arm in front (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1318,8 +1451,21 @@
           <t>Warm-up: mobility</t>
         </is>
       </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (full)
+Hip: Leg behind you (full)
+Ankle: Balance and uneven ground (partial)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest
+Hip: Leg behind you</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1371,8 +1517,20 @@
           <t>Warm-up: mobility</t>
         </is>
       </c>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Turn the hip (full)
+Hip: Leg out to the side (partial)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Turn the hip
+Hip: Leg out to the side</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1424,8 +1582,22 @@
           <t>Warm-up: mobility, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Bend forward (full)
+Lower back: Arch your back (full)
+Wrist: Weight on your hands (partial)
+Knee: Kneel (full)</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Bend forward
+Lower back: Arch your back</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1477,8 +1649,18 @@
           <t>Warm-up: mobility</t>
         </is>
       </c>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Twist (full)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Twist</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1532,8 +1714,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Weight on your hands (full)</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1586,8 +1780,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Weight on your hands (partial)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1640,8 +1846,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Weight on your hands (full)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1694,8 +1912,21 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Shoulder: Raise arm in front (partial)
+Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1748,8 +1979,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1801,8 +2044,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (full)
+Shoulder: Push (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1854,8 +2109,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1908,8 +2174,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1962,8 +2240,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (partial)
+Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2016,8 +2306,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2071,8 +2373,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (partial)
+Elbow: Straighten elbow with weight (partial)
+Wrist: Weight on your hands (full)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2125,8 +2439,22 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead (full)
+Shoulder: Raise arm to the side (full)
+Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2177,8 +2505,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2231,8 +2570,22 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (full)
+Shoulder: Turn arm outward (full)
+Shoulder: Raise arm to the side (partial)
+Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2286,8 +2639,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (full)
+Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2340,8 +2705,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (full)
+Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2394,8 +2771,21 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead (full)
+Shoulder: Pull (full)
+Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2448,8 +2838,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (full)
+Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2501,8 +2903,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Carry weight (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2554,8 +2967,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Arch your back (full)
+Shoulder: Arm overhead (partial)
+Hip: Leg behind you (partial)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Arch your back</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2608,8 +3033,21 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead (partial)
+Hip: Leg behind you (partial)
+Wrist: Weight on your hands (partial)
+Knee: Kneel (full)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2661,8 +3099,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2714,8 +3163,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2766,8 +3226,21 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead (full)
+Elbow: Straighten elbow with weight (full)
+Elbow: Bend elbow with weight (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2820,8 +3293,21 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Reach behind your back (full)
+Shoulder: Push (full)
+Elbow: Straighten elbow with weight (full)
+Wrist: Weight on your hands (full)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Reach behind your back</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2872,8 +3358,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Elbow: Straighten elbow with weight (full)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2924,8 +3421,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Wrist: Bend wrist down (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2979,8 +3487,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K40" s="6" t="n"/>
-      <c r="L40" s="6" t="n"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (hold, no movement)
+Wrist: Weight on your hands (partial)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3032,8 +3551,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead (partial)
+Hip: Knee toward chest (full)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3085,8 +3615,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Neck: Look down (partial)
+Lower back: Bend forward (partial)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3138,8 +3679,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Bend forward (full)
+Hip: Knee toward chest (full)</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3192,8 +3744,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (hold, no movement)
+Hip: Leg out to the side (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3245,8 +3808,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K45" s="6" t="n"/>
-      <c r="L45" s="6" t="n"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (partial)
+Lower back: Twist (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3299,8 +3873,21 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)
+Hip: Deep squat (full)
+Ankle: Knee over toes (full)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep
+Hip: Deep squat</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3353,8 +3940,22 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K47" s="6" t="n"/>
-      <c r="L47" s="6" t="n"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)
+Hip: Deep squat (full)
+Ankle: Knee over toes (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep
+Hip: Deep squat</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3406,8 +4007,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (partial)
+Hip: Knee toward chest (partial)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="n"/>
+      <c r="N48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3460,8 +4072,22 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)
+Hip: Leg behind you (full)
+Hip: Stand on one leg (partial)
+Ankle: Knee over toes (full)
+Ankle: Balance and uneven ground (partial)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3513,8 +4139,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)
+Hip: Deep squat (full)</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep
+Hip: Deep squat</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="n"/>
+      <c r="N50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3567,8 +4205,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Leg behind you (full)
+Lower back: Arch your back (partial)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3621,8 +4270,20 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (full)
+Lower back: Lift from the floor (full)
+Wrist: Grip tight (full)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -3674,8 +4335,18 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3726,8 +4397,19 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Tiptoe (full)
+Ankle: Balance and uneven ground (partial)</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Tiptoe</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n"/>
+      <c r="N54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -3779,8 +4461,18 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (full)</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="n"/>
+      <c r="N55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3831,8 +4523,18 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="n"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Leg across (full)</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="n"/>
+      <c r="N56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -3883,8 +4585,18 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K57" s="6" t="n"/>
-      <c r="L57" s="6" t="n"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Knee over toes (full)</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Knee over toes</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="n"/>
+      <c r="N57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3936,8 +4648,18 @@
           <t>Main work</t>
         </is>
       </c>
-      <c r="K58" s="6" t="n"/>
-      <c r="L58" s="6" t="n"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Straighten with effort (partial)</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="n"/>
+      <c r="N58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3989,8 +4711,20 @@
           <t>Main work, Finisher: cardio</t>
         </is>
       </c>
-      <c r="K59" s="6" t="n"/>
-      <c r="L59" s="6" t="n"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Stairs (full)
+Hip: Knee toward chest (partial)
+Ankle: Balance and uneven ground (partial)</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="n"/>
+      <c r="N59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4043,8 +4777,19 @@
           <t>Main work, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Balance and uneven ground (full)
+Hip: Stand on one leg (full)</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="n"/>
+      <c r="N60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -4097,8 +4842,20 @@
           <t>Finisher: cardio</t>
         </is>
       </c>
-      <c r="K61" s="6" t="n"/>
-      <c r="L61" s="6" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (full)
+Wrist: Weight on your hands (full)
+Hip: Knee toward chest (full)</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="n"/>
+      <c r="N61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -4152,8 +4909,20 @@
           <t>Cool-down: stretch, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="n"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward (full)
+Shoulder: Raise arm to the side (full)</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward
+Shoulder: Raise arm to the side</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="n"/>
+      <c r="N62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -4205,8 +4974,18 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="6" t="n"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (partial)</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="n"/>
+      <c r="N63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -4258,8 +5037,19 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="n"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Arm overhead (full)
+Elbow: Bend elbow with weight (full)</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="n"/>
+      <c r="N64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -4312,8 +5102,20 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K65" s="6" t="n"/>
-      <c r="L65" s="6" t="n"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (full)
+Hip: Leg behind you (partial)
+Ankle: Balance and uneven ground (partial)</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="n"/>
+      <c r="N65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -4365,8 +5167,19 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (full)
+Lower back: Bend forward (partial)</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="n"/>
+      <c r="N66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -4418,8 +5231,19 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K67" s="6" t="n"/>
-      <c r="L67" s="6" t="n"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Turn the hip (full)
+Knee: Bend the knee deep (partial)</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Turn the hip</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="n"/>
+      <c r="N67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -4471,8 +5295,18 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="6" t="n"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Knee over toes (full)</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Knee over toes</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="n"/>
+      <c r="N68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -4525,8 +5359,22 @@
           <t>Cool-down: stretch, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="n"/>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Kneel (full)
+Knee: Bend the knee deep (full)
+Hip: Deep squat (full)
+Lower back: Bend forward (partial)
+Shoulder: Arm overhead (partial)</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="n"/>
+      <c r="N69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -4578,8 +5426,19 @@
           <t>Cool-down: stretch, Finisher: mobility</t>
         </is>
       </c>
-      <c r="K70" s="6" t="n"/>
-      <c r="L70" s="6" t="n"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Kneel (full)
+Hip: Leg behind you (full)</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Leg behind you</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="n"/>
+      <c r="N70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -4630,8 +5489,18 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="n"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Neck: Tilt your head to the side (full)</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Neck: Tilt your head to the side</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="n"/>
+      <c r="N71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -4683,8 +5552,19 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K72" s="6" t="n"/>
-      <c r="L72" s="6" t="n"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Lean to the side (full)
+Shoulder: Arm overhead (full)</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Lean to the side</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="n"/>
+      <c r="N72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -4736,8 +5616,18 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="n"/>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (partial)</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="n"/>
+      <c r="N73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -4789,8 +5679,19 @@
           <t>Cool-down: stretch</t>
         </is>
       </c>
-      <c r="K74" s="6" t="n"/>
-      <c r="L74" s="6" t="n"/>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Reach behind your back (full)
+Elbow: Straighten elbow with weight (full)</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Reach behind your back</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="n"/>
+      <c r="N74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -4841,13 +5742,525 @@
           <t>Cool-down: breathing</t>
         </is>
       </c>
-      <c r="K75" s="6" t="n"/>
-      <c r="L75" s="6" t="n"/>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="n"/>
+      <c r="N75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>iso_shoulder_external_rotation</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Wall press, arm turning out</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Rear shoulders (Deltoid · rear head): primary, 0.6
+Front shoulders (Deltoid · front head): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Elbow bent at your side, back of the hand against a wall. Press gently outward without moving. Hold 20–30 s.</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="n"/>
+      <c r="N76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>iso_shoulder_internal_rotation</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Doorframe press, arm turning in</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Front shoulders (Deltoid · front head): primary, 0.5
+Chest (Pectoralis major): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Elbow bent at your side, palm against a doorframe. Press gently inward without moving. Hold 20–30 s.</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="n"/>
+      <c r="N77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>iso_shoulder_abduction</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Wall press, arm to the side</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Front shoulders (Deltoid · front head): primary, 0.6</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Stand side-on to a wall, elbow bent, outer elbow against it. Press gently out without moving. Hold 20–30 s.</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="n"/>
+      <c r="N78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>iso_shoulder_flexion</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Wall press, arm forward</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Front shoulders (Deltoid · front head): primary, 0.6</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Face a wall, elbow bent, fist against it. Press gently forward without moving. Hold 20–30 s.</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="n"/>
+      <c r="N79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>band_external_rotation</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Band external rotation</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Rear shoulders (Deltoid · rear head): primary, 0.6
+Upper back (Rhomboids and middle trapezius): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Bands</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Elbow bent at your side, band in hand. Turn the forearm out slowly, only in the pain-free range.</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="n"/>
+      <c r="N80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>quad_set</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Thigh squeeze</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Quads (Quadriceps): primary, 0.6
+Knees (Muscles around the knee): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Sit with the leg straight. Tighten the front of the thigh, pressing the knee down. Hold 10 s, relax.</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Straighten with effort (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="n"/>
+      <c r="N81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>chin_tuck</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Chin tuck</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Traps (Trapezius): primary, 0.5
+Upper back (Rhomboids and middle trapezius): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Sit tall. Slide the chin straight back, making a double chin, without tilting. Hold 5 s.</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Main work, Warm-up: mobility · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Neck: Look down (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="n"/>
+      <c r="N82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>iso_wrist_extension</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Wrist press, back of hand</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Forearms (Wrist flexors and extensors): primary, 0.7</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Forearm on a table, palm down. Press the back of the hand up into your other hand without moving. Hold 20–30 s.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Wrist: Weight on your hands (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="n"/>
+      <c r="N83" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L75"/>
+  <autoFilter ref="A1:N83"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
+    <dataValidation sqref="M2:M83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4861,7 +6274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4872,8 +6285,9 @@
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -4919,10 +6333,15 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>Joint movements (range)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
           <t>Approve / Fix (Aprovado/Corrigir)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Comment (Comentário)</t>
         </is>
@@ -4969,8 +6388,14 @@
           <t>Strengthen: Quads, Glutes</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Knee: Bend the knee deep (partial)
+Hip: Knee toward chest (partial)</t>
+        </is>
+      </c>
       <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -5013,8 +6438,14 @@
           <t>Balance: Hips, Glutes</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Ankle: Balance and uneven ground (full)
+Hip: Stand on one leg (full)</t>
+        </is>
+      </c>
       <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -5057,8 +6488,14 @@
           <t>Strengthen: Glutes, Hamstrings</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Leg behind you (hold, no movement)
+Lower back: Arch your back (partial)</t>
+        </is>
+      </c>
       <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5101,8 +6538,14 @@
           <t>Strengthen: Upper abs, Lower abs, Obliques</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Push (hold, no movement)
+Wrist: Weight on your hands (partial)</t>
+        </is>
+      </c>
       <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -5145,12 +6588,1210 @@
           <t>Mobility: Front shoulders, Upper back</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Reach behind your back (full)
+Shoulder: Arm overhead (full)</t>
+        </is>
+      </c>
       <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Approve,Fix"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Movement (key)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Shown to the user</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Everyday example</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Approve / Fix (Aprovado/Corrigir)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comment (Comentário)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.flexion</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Raise arm in front</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Reaching a high shelf in front of you</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.abduction</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Raise arm to the side</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Reaching sideways for something on the counter</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.reach_behind</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Reach behind your back</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Tucking in a shirt, fastening a bra</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.external_rotation</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Turn arm outward</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Brushing your hair, throwing a ball</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.internal_rotation</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Turn arm inward</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Reaching for your back pocket</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.overhead</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Arm overhead</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Putting a box on a top shelf, washing your hair</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.push</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Pushing a heavy door, getting up from a chair with your arms</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.pull</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Opening a heavy door, pulling a suitcase</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>shoulder.carry</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Carry weight</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Carrying grocery bags</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Elbow</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>elbow.flexion</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Bend elbow with weight</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Lifting a pot</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Elbow</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>elbow.extension</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Straighten elbow with weight</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Pushing up from a chair, pushing a cart</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Wrist</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>wrist.extension_load</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Weight on your hands</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Pushing up from the floor</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Wrist</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>wrist.flexion</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Bend wrist down</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Pouring from a jug</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Wrist</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>wrist.grip</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Grip tight</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Opening a jar, holding a heavy bag</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Wrist</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>wrist.rotation</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Twist the forearm</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Turning a key or a doorknob</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Neck</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>neck.flexion</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Look down</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Reading a phone in your lap</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Neck</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>neck.extension</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Look up</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Looking at a high shelf or the ceiling</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Neck</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>neck.rotation</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Turn your head</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Checking the blind spot when driving</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Neck</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>neck.side_bend</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Tilt your head to the side</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Holding a phone between ear and shoulder</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>lower_back.flexion</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Bend forward</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Putting on socks, loading the dishwasher</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>lower_back.extension</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Arch your back</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Reaching up to a high shelf</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>lower_back.rotation</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Twist</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Turning to grab something from the back seat</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>lower_back.side_bend</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Lean to the side</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Picking up a bag at your side</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>lower_back.lift</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Lift from the floor</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Picking up a laundry basket or a child</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>hip.flexion</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Knee toward chest</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Putting on shoes, getting into a car</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>hip.extension</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Leg behind you</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Long strides, walking up a hill</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>hip.abduction</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Leg out to the side</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Getting out of a car, stepping sideways</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>hip.adduction</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Leg across</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Crossing your legs</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>hip.rotation</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Turn the hip</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Sitting cross-legged, pivoting on one foot</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>hip.deep_squat</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Deep squat</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Picking something up from the floor, a low chair</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>hip.single_leg</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Stand on one leg</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Putting on pants standing, stairs</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>knee.deep_bend</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Bend the knee deep</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Squatting, sitting on a low sofa</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>knee.kneel</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Kneel</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Kneeling to clean or garden</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>knee.straighten_load</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Straighten with effort</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Kicking a ball, standing up from a chair</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>knee.stairs</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Stairs</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Going up or down stairs</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>knee.pivot</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Twist on the knee</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Turning quickly with the foot planted</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>knee.impact</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Jump or run</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Jogging, jumping</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>ankle.dorsiflexion</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Knee over toes</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Squatting, walking downhill</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>ankle.plantarflexion</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Tiptoe</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Reaching up on your toes</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>ankle.balance</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Balance and uneven ground</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Walking on grass or cobblestones</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>ankle.impact</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Jump or run</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Jogging, jumping</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Red flags</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>No plan, see a doctor, if any applies:</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>It started after a fall, a blow or an accident
+Strong pain at night that wakes you up
+Tingling, numbness or pins and needles
+Weakness: you can't lift the arm, or the leg gives way
+Swelling, redness or heat
+Fever or feeling unwell</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Recovery phase 1</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Calm it down: gentle holds and pain-free range.</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Front shoulders, Rear shoulders; Elbow: Forearms; Wrist: Forearms; Neck: Traps, Upper back; Lower back: Abs, Glutes; Hip: Glutes, Hips; Knee: Quads; Ankle: Calves, Shins</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Recovery phase 2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Strengthen: build strength in the pain-free range.</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Rear shoulders, Upper back, Front shoulders; Elbow: Forearms, Biceps, Triceps; Wrist: Forearms; Neck: Upper back, Traps, Rear shoulders; Lower back: Glutes, Obliques, Lower back; Hip: Glutes, Hips, Inner thighs; Knee: Quads, Glutes, Hamstrings; Ankle: Calves, Shins</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Recovery phase 3</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Progress: more range and load, step by step.</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Front shoulders, Upper back, Chest, Lats; Elbow: Biceps, Triceps, Forearms; Wrist: Forearms, Biceps; Neck: Upper back, Traps, Front shoulders; Lower back: Lower back, Glutes, Hamstrings; Hip: Glutes, Quads, Hamstrings; Knee: Quads, Glutes, Calves; Ankle: Calves, Shins, Quads</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Traffic light</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0–3 green: moving on. 4–5 yellow: staying. Over 5, or clearly worse the next morning: red, one step back.</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Levels 1–6: green +1, yellow hold, red −1. Phase 1 = levels 1–2, 2 = 3–4, 3 = 5–6. Pain 7+ leaves the whole joint out; holds and shorter range only at pain 5 or less.</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Physical therapist</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>See a physical therapist</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Recommended when the weekly retest is worse than at the start, or no better after 3 weeks.</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -5768,8 +5768,8 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Rear shoulders (Deltoid · rear head): primary, 0.6
-Front shoulders (Deltoid · front head): secondary, 0.4</t>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Rear shoulders (Deltoid · rear head): secondary, 0.4</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Front shoulders (Deltoid · front head): primary, 0.5
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
 Chest (Pectoralis major): secondary, 0.3</t>
         </is>
       </c>
@@ -5894,7 +5894,8 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Front shoulders (Deltoid · front head): primary, 0.6</t>
+          <t>Front shoulders (Deltoid · front head): primary, 0.6
+Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): secondary, 0.5</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -5956,7 +5957,8 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Front shoulders (Deltoid · front head): primary, 0.6</t>
+          <t>Front shoulders (Deltoid · front head): primary, 0.6
+Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): secondary, 0.4</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -6018,7 +6020,8 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Rear shoulders (Deltoid · rear head): primary, 0.6
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Rear shoulders (Deltoid · rear head): secondary, 0.4
 Upper back (Rhomboids and middle trapezius): secondary, 0.3</t>
         </is>
       </c>
@@ -7687,7 +7690,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Shoulder: Front shoulders, Rear shoulders; Elbow: Forearms; Wrist: Forearms; Neck: Traps, Upper back; Lower back: Abs, Glutes; Hip: Glutes, Hips; Knee: Quads; Ankle: Calves, Shins</t>
+          <t>Shoulder: Rotator cuff, Rear shoulders; Elbow: Forearms; Wrist: Forearms; Neck: Traps, Upper back; Lower back: Abs, Glutes; Hip: Glutes, Hips; Knee: Quads; Ankle: Calves, Shins</t>
         </is>
       </c>
       <c r="E44" s="6" t="n"/>
@@ -7711,7 +7714,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Shoulder: Rear shoulders, Upper back, Front shoulders; Elbow: Forearms, Biceps, Triceps; Wrist: Forearms; Neck: Upper back, Traps, Rear shoulders; Lower back: Glutes, Obliques, Lower back; Hip: Glutes, Hips, Inner thighs; Knee: Quads, Glutes, Hamstrings; Ankle: Calves, Shins</t>
+          <t>Shoulder: Rotator cuff, Rear shoulders, Upper back; Elbow: Forearms, Biceps, Triceps; Wrist: Forearms; Neck: Upper back, Traps, Rear shoulders; Lower back: Glutes, Obliques, Lower back; Hip: Glutes, Hips, Inner thighs; Knee: Quads, Glutes, Hamstrings; Ankle: Calves, Shins</t>
         </is>
       </c>
       <c r="E45" s="6" t="n"/>
@@ -7735,7 +7738,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Shoulder: Front shoulders, Upper back, Chest, Lats; Elbow: Biceps, Triceps, Forearms; Wrist: Forearms, Biceps; Neck: Upper back, Traps, Front shoulders; Lower back: Lower back, Glutes, Hamstrings; Hip: Glutes, Quads, Hamstrings; Knee: Quads, Glutes, Calves; Ankle: Calves, Shins, Quads</t>
+          <t>Shoulder: Front shoulders, Rotator cuff, Upper back, Chest; Elbow: Biceps, Triceps, Forearms; Wrist: Forearms, Biceps; Neck: Upper back, Traps, Front shoulders; Lower back: Lower back, Glutes, Hamstrings; Hip: Glutes, Quads, Hamstrings; Knee: Quads, Glutes, Calves; Ankle: Calves, Shins, Quads</t>
         </is>
       </c>
       <c r="E46" s="6" t="n"/>

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Movements" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$N$743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$N$748</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTA(Exercises!$A$2:$A$743)</f>
+        <f>COUNTA(Exercises!$A$2:$A$748)</f>
         <v/>
       </c>
     </row>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>COUNTIF(Exercises!$M$2:$M$743,"Approve")</f>
+        <f>COUNTIF(Exercises!$M$2:$M$748,"Approve")</f>
         <v/>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>COUNTIF(Exercises!$M$2:$M$743,"Fix")</f>
+        <f>COUNTIF(Exercises!$M$2:$M$748,"Fix")</f>
         <v/>
       </c>
     </row>
@@ -856,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N743"/>
+  <dimension ref="A1:N748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28104,7 +28104,7 @@
       </c>
       <c r="F419" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G419" s="5" t="inlineStr">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="F420" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G420" s="5" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="F421" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G421" s="5" t="inlineStr">
@@ -28889,7 +28889,7 @@
       </c>
       <c r="F431" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G431" s="5" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="F432" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G432" s="5" t="inlineStr">
@@ -29080,7 +29080,7 @@
       </c>
       <c r="F434" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G434" s="5" t="inlineStr">
@@ -29207,7 +29207,7 @@
       </c>
       <c r="F436" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G436" s="5" t="inlineStr">
@@ -29269,7 +29269,7 @@
       </c>
       <c r="F437" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G437" s="5" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="F439" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G439" s="5" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="F440" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G440" s="5" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="F441" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G441" s="5" t="inlineStr">
@@ -29645,7 +29645,7 @@
       </c>
       <c r="F443" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G443" s="5" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="F447" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G447" s="5" t="inlineStr">
@@ -30669,7 +30669,7 @@
       </c>
       <c r="F459" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G459" s="5" t="inlineStr">
@@ -30798,7 +30798,7 @@
       </c>
       <c r="F461" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G461" s="5" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="F462" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G462" s="5" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="F464" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G464" s="5" t="inlineStr">
@@ -31121,7 +31121,7 @@
       </c>
       <c r="F466" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G466" s="5" t="inlineStr">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="F467" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G467" s="5" t="inlineStr">
@@ -31250,7 +31250,7 @@
       </c>
       <c r="F468" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G468" s="5" t="inlineStr">
@@ -31312,7 +31312,7 @@
       </c>
       <c r="F469" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G469" s="5" t="inlineStr">
@@ -31505,7 +31505,7 @@
       </c>
       <c r="F472" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G472" s="5" t="inlineStr">
@@ -31568,7 +31568,7 @@
       </c>
       <c r="F473" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G473" s="5" t="inlineStr">
@@ -31631,7 +31631,7 @@
       </c>
       <c r="F474" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G474" s="5" t="inlineStr">
@@ -31695,7 +31695,7 @@
       </c>
       <c r="F475" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G475" s="5" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="F476" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G476" s="5" t="inlineStr">
@@ -31823,7 +31823,7 @@
       </c>
       <c r="F477" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G477" s="5" t="inlineStr">
@@ -31888,7 +31888,7 @@
       </c>
       <c r="F478" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G478" s="5" t="inlineStr">
@@ -31951,7 +31951,7 @@
       </c>
       <c r="F479" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G479" s="5" t="inlineStr">
@@ -32017,7 +32017,7 @@
       </c>
       <c r="F480" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G480" s="5" t="inlineStr">
@@ -32082,7 +32082,7 @@
       </c>
       <c r="F481" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G481" s="5" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="F484" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G484" s="5" t="inlineStr">
@@ -32340,7 +32340,7 @@
       </c>
       <c r="F485" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G485" s="5" t="inlineStr">
@@ -32403,7 +32403,7 @@
       </c>
       <c r="F486" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G486" s="5" t="inlineStr">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="F487" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G487" s="5" t="inlineStr">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="F488" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G488" s="5" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="F489" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G489" s="5" t="inlineStr">
@@ -32656,7 +32656,7 @@
       </c>
       <c r="F490" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G490" s="5" t="inlineStr">
@@ -32719,7 +32719,7 @@
       </c>
       <c r="F491" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G491" s="5" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="F492" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G492" s="5" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="F493" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G493" s="5" t="inlineStr">
@@ -32907,7 +32907,7 @@
       </c>
       <c r="F494" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G494" s="5" t="inlineStr">
@@ -32969,7 +32969,7 @@
       </c>
       <c r="F495" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G495" s="5" t="inlineStr">
@@ -33031,7 +33031,7 @@
       </c>
       <c r="F496" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G496" s="5" t="inlineStr">
@@ -33093,7 +33093,7 @@
       </c>
       <c r="F497" s="5" t="inlineStr">
         <is>
-          <t>9+ (kids)</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G497" s="5" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="J504" s="5" t="inlineStr">
         <is>
-          <t>Cool-down: walk, Warm-up: easy cardio</t>
+          <t>Cool-down: walk</t>
         </is>
       </c>
       <c r="K504" s="5" t="inlineStr">
@@ -48888,10 +48888,326 @@
       <c r="M743" s="6" t="n"/>
       <c r="N743" s="6" t="n"/>
     </row>
+    <row r="744">
+      <c r="A744" s="5" t="inlineStr">
+        <is>
+          <t>sv_seated_backrest_chest_opener</t>
+        </is>
+      </c>
+      <c r="B744" s="5" t="inlineStr">
+        <is>
+          <t>Seated backrest chest opener</t>
+        </is>
+      </c>
+      <c r="C744" s="5" t="inlineStr">
+        <is>
+          <t>Mid chest (Pectoralis major · sternal head): primary, 0.8
+Front shoulders (Deltoid · front head): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D744" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E744" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F744" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G744" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H744" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder</t>
+        </is>
+      </c>
+      <c r="I744" s="5" t="inlineStr">
+        <is>
+          <t>Sit tall, hold the sides of the backrest behind you and gently lift your chest until you feel a stretch.</t>
+        </is>
+      </c>
+      <c r="J744" s="5" t="inlineStr">
+        <is>
+          <t>Cool-down: stretch</t>
+        </is>
+      </c>
+      <c r="K744" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Reach behind your back (partial)</t>
+        </is>
+      </c>
+      <c r="L744" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M744" s="6" t="n"/>
+      <c r="N744" s="6" t="n"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="5" t="inlineStr">
+        <is>
+          <t>sv_seated_knee_hug_glute</t>
+        </is>
+      </c>
+      <c r="B745" s="5" t="inlineStr">
+        <is>
+          <t>Seated knee hug</t>
+        </is>
+      </c>
+      <c r="C745" s="5" t="inlineStr">
+        <is>
+          <t>Glutes (Gluteus maximus and medius): primary, 0.8
+Lower back (Erector spinae): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D745" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E745" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F745" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G745" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H745" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="I745" s="5" t="inlineStr">
+        <is>
+          <t>Sit tall, lift one knee and hug it gently toward your chest; hold, breathe, then switch sides.</t>
+        </is>
+      </c>
+      <c r="J745" s="5" t="inlineStr">
+        <is>
+          <t>Cool-down: stretch</t>
+        </is>
+      </c>
+      <c r="K745" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Knee toward chest (partial)</t>
+        </is>
+      </c>
+      <c r="L745" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M745" s="6" t="n"/>
+      <c r="N745" s="6" t="n"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="5" t="inlineStr">
+        <is>
+          <t>sv_seated_cross_knee_glute</t>
+        </is>
+      </c>
+      <c r="B746" s="5" t="inlineStr">
+        <is>
+          <t>Seated cross-knee glute pull</t>
+        </is>
+      </c>
+      <c r="C746" s="5" t="inlineStr">
+        <is>
+          <t>Glutes (Gluteus maximus and medius): primary, 0.8
+Hips (Hip flexors): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D746" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E746" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F746" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G746" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H746" s="5" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="I746" s="5" t="inlineStr">
+        <is>
+          <t>Sit tall, cross one knee over the other and pull it gently toward the opposite shoulder; hold, then switch.</t>
+        </is>
+      </c>
+      <c r="J746" s="5" t="inlineStr">
+        <is>
+          <t>Cool-down: stretch</t>
+        </is>
+      </c>
+      <c r="K746" s="5" t="inlineStr">
+        <is>
+          <t>Hip: Leg across (partial)</t>
+        </is>
+      </c>
+      <c r="L746" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M746" s="6" t="n"/>
+      <c r="N746" s="6" t="n"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="5" t="inlineStr">
+        <is>
+          <t>sv_seated_sky_reach_belly</t>
+        </is>
+      </c>
+      <c r="B747" s="5" t="inlineStr">
+        <is>
+          <t>Seated sky reach</t>
+        </is>
+      </c>
+      <c r="C747" s="5" t="inlineStr">
+        <is>
+          <t>Upper abs (Rectus abdominis · upper): primary, 0.7
+Lats (Latissimus dorsi): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D747" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E747" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F747" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G747" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H747" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="I747" s="5" t="inlineStr">
+        <is>
+          <t>Sit tall, interlace your fingers, reach up and slightly back, feel the front of your belly lengthen; breathe.</t>
+        </is>
+      </c>
+      <c r="J747" s="5" t="inlineStr">
+        <is>
+          <t>Cool-down: stretch</t>
+        </is>
+      </c>
+      <c r="K747" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Arch your back (partial)
+Shoulder: Arm overhead (partial)</t>
+        </is>
+      </c>
+      <c r="L747" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M747" s="6" t="n"/>
+      <c r="N747" s="6" t="n"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="5" t="inlineStr">
+        <is>
+          <t>sv_seated_hands_on_knees_lift</t>
+        </is>
+      </c>
+      <c r="B748" s="5" t="inlineStr">
+        <is>
+          <t>Seated chest-lift belly stretch</t>
+        </is>
+      </c>
+      <c r="C748" s="5" t="inlineStr">
+        <is>
+          <t>Lower abs (Rectus abdominis · lower): primary, 0.7
+Hips (Hip flexors): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D748" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E748" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F748" s="5" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="G748" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H748" s="5" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="I748" s="5" t="inlineStr">
+        <is>
+          <t>Hands on knees, press them gently, lift your chest and look slightly up to stretch the lower belly; breathe.</t>
+        </is>
+      </c>
+      <c r="J748" s="5" t="inlineStr">
+        <is>
+          <t>Cool-down: stretch</t>
+        </is>
+      </c>
+      <c r="K748" s="5" t="inlineStr">
+        <is>
+          <t>Lower back: Arch your back (partial)</t>
+        </is>
+      </c>
+      <c r="L748" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M748" s="6" t="n"/>
+      <c r="N748" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N743"/>
+  <autoFilter ref="A1:N748"/>
   <dataValidations count="1">
-    <dataValidation sqref="M2:M743" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
+    <dataValidation sqref="M2:M748" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -21082,7 +21082,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -21148,7 +21148,7 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="G327" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G332" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H332" s="5" t="inlineStr">
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G423" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H423" s="5" t="inlineStr">
@@ -28828,7 +28828,7 @@
       </c>
       <c r="G430" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support, Seated</t>
+          <t>Standing, Seated</t>
         </is>
       </c>
       <c r="H430" s="5" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="G673" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H673" s="5" t="inlineStr">
@@ -44917,7 +44917,7 @@
       </c>
       <c r="G682" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H682" s="5" t="inlineStr">
@@ -44984,7 +44984,7 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
@@ -47174,7 +47174,7 @@
       </c>
       <c r="G717" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H717" s="5" t="inlineStr">
@@ -47497,7 +47497,7 @@
       </c>
       <c r="G722" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H722" s="5" t="inlineStr">
@@ -47564,7 +47564,7 @@
       </c>
       <c r="G723" s="5" t="inlineStr">
         <is>
-          <t>Standing, With support</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H723" s="5" t="inlineStr">
@@ -48071,7 +48071,7 @@
       </c>
       <c r="G731" s="5" t="inlineStr">
         <is>
-          <t>With support, Standing</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="H731" s="5" t="inlineStr">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -1228,7 +1228,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Exercise bike</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>Flat bench</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Chest press machine</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Chest press machine</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>Adjustable bench</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Lat pulldown</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Seated row (cable)</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>Flat bench</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Leg press</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Leg curl machine</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>Flat bench</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Adjustable bench</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Chest press machine</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Barbell, Bench</t>
+          <t>Barbell, Adjustable bench</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Cable, Bench</t>
+          <t>Cable station, Adjustable bench</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Barbell, Bench</t>
+          <t>Barbell, Flat bench</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Pec deck</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Assisted pull-up / dip machine</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Dip station</t>
         </is>
       </c>
       <c r="E220" s="5" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Barbell, Bench</t>
+          <t>Barbell, Adjustable bench</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Shoulder press machine</t>
         </is>
       </c>
       <c r="E223" s="5" t="n">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Lateral raise machine</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E226" s="5" t="n">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Pec deck</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Seated row (cable)</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Row machine</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E238" s="5" t="n">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Barbell</t>
+          <t>Barbell, Squat rack</t>
         </is>
       </c>
       <c r="E239" s="5" t="n">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Assisted pull-up / dip machine</t>
         </is>
       </c>
       <c r="E242" s="5" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E243" s="5" t="n">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E244" s="5" t="n">
@@ -16829,7 +16829,7 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E245" s="5" t="n">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Preacher curl machine</t>
         </is>
       </c>
       <c r="E247" s="5" t="n">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E248" s="5" t="n">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Barbell, Bench</t>
+          <t>Barbell, Flat bench</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
@@ -17473,7 +17473,7 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Barbell, Bench</t>
+          <t>Barbell, Flat bench</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E298" s="5" t="n">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E299" s="5" t="n">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E300" s="5" t="n">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E302" s="5" t="n">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E303" s="5" t="n">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E305" s="5" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E306" s="5" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E307" s="5" t="n">
@@ -20880,7 +20880,7 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E308" s="5" t="n">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E309" s="5" t="n">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E310" s="5" t="n">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E312" s="5" t="n">
@@ -21206,7 +21206,7 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E313" s="5" t="n">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Leg extension machine</t>
         </is>
       </c>
       <c r="E319" s="5" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Leg curl machine</t>
         </is>
       </c>
       <c r="E320" s="5" t="n">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Hip abductor / adductor</t>
         </is>
       </c>
       <c r="E321" s="5" t="n">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Hip abductor / adductor</t>
         </is>
       </c>
       <c r="E322" s="5" t="n">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Barbell</t>
+          <t>Barbell, Squat rack</t>
         </is>
       </c>
       <c r="E323" s="5" t="n">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Barbell, Bench</t>
+          <t>Barbell, Flat bench</t>
         </is>
       </c>
       <c r="E324" s="5" t="n">
@@ -21984,7 +21984,7 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E325" s="5" t="n">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Calf raise machine</t>
         </is>
       </c>
       <c r="E326" s="5" t="n">
@@ -22113,7 +22113,7 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E327" s="5" t="n">
@@ -22178,7 +22178,7 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Back extension bench</t>
         </is>
       </c>
       <c r="E329" s="5" t="n">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E330" s="5" t="n">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Ab crunch machine</t>
         </is>
       </c>
       <c r="E331" s="5" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E332" s="5" t="n">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E426" s="5" t="n">
@@ -28876,7 +28876,7 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E431" s="5" t="n">
@@ -28941,7 +28941,7 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E432" s="5" t="n">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E440" s="5" t="n">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E441" s="5" t="n">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E449" s="5" t="n">
@@ -31177,7 +31177,7 @@
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E467" s="5" t="n">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>Flat bench</t>
         </is>
       </c>
       <c r="E477" s="5" t="n">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E481" s="5" t="n">
@@ -32202,7 +32202,7 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E483" s="5" t="n">
@@ -32267,7 +32267,7 @@
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E484" s="5" t="n">
@@ -32526,7 +32526,7 @@
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E488" s="5" t="n">
@@ -32656,7 +32656,7 @@
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E490" s="5" t="n">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E501" s="5" t="n">
@@ -33410,7 +33410,7 @@
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E502" s="5" t="n">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Exercise bike</t>
         </is>
       </c>
       <c r="E511" s="5" t="n">
@@ -34687,7 +34687,7 @@
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Rowing machine</t>
         </is>
       </c>
       <c r="E522" s="5" t="n">
@@ -34754,7 +34754,7 @@
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Exercise bike</t>
         </is>
       </c>
       <c r="E523" s="5" t="n">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E569" s="5" t="n">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E570" s="5" t="n">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="D613" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E613" s="5" t="n">
@@ -40567,7 +40567,7 @@
       </c>
       <c r="D614" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Mini bands</t>
         </is>
       </c>
       <c r="E614" s="5" t="n">
@@ -40945,7 +40945,7 @@
       </c>
       <c r="D620" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E620" s="5" t="n">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E621" s="5" t="n">
@@ -44530,7 +44530,7 @@
       </c>
       <c r="D676" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E676" s="5" t="n">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>Kettlebell</t>
+          <t>Kettlebells</t>
         </is>
       </c>
       <c r="E679" s="5" t="n">
@@ -45231,7 +45231,7 @@
       </c>
       <c r="D687" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E687" s="5" t="n">
@@ -45295,7 +45295,7 @@
       </c>
       <c r="D688" s="5" t="inlineStr">
         <is>
-          <t>Kettlebell, Bench</t>
+          <t>Kettlebells, Flat bench</t>
         </is>
       </c>
       <c r="E688" s="5" t="n">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="D701" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E701" s="5" t="n">
@@ -46268,7 +46268,7 @@
       </c>
       <c r="D703" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E703" s="5" t="n">
@@ -46333,7 +46333,7 @@
       </c>
       <c r="D704" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E704" s="5" t="n">
@@ -46399,7 +46399,7 @@
       </c>
       <c r="D705" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E705" s="5" t="n">
@@ -46528,7 +46528,7 @@
       </c>
       <c r="D707" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E707" s="5" t="n">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="D710" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E710" s="5" t="n">
@@ -46845,7 +46845,7 @@
       </c>
       <c r="D712" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E712" s="5" t="n">
@@ -47036,7 +47036,7 @@
       </c>
       <c r="D715" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E715" s="5" t="n">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="D720" s="5" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>Flat bench</t>
         </is>
       </c>
       <c r="E720" s="5" t="n">
@@ -47487,7 +47487,7 @@
       </c>
       <c r="D722" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E722" s="5" t="n">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="D723" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E723" s="5" t="n">
@@ -47618,7 +47618,7 @@
       </c>
       <c r="D724" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E724" s="5" t="n">
@@ -47810,7 +47810,7 @@
       </c>
       <c r="D727" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E727" s="5" t="n">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="D728" s="5" t="inlineStr">
         <is>
-          <t>Kettlebell</t>
+          <t>Kettlebells</t>
         </is>
       </c>
       <c r="E728" s="5" t="n">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="D730" s="5" t="inlineStr">
         <is>
-          <t>Bands, Mat</t>
+          <t>Mini bands, Mat</t>
         </is>
       </c>
       <c r="E730" s="5" t="n">
@@ -48070,7 +48070,7 @@
       </c>
       <c r="D731" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E731" s="5" t="n">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="D732" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E732" s="5" t="n">
@@ -48196,7 +48196,7 @@
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable station</t>
         </is>
       </c>
       <c r="E733" s="5" t="n">
@@ -48260,7 +48260,7 @@
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>Bands, Mat</t>
+          <t>Mini bands, Mat</t>
         </is>
       </c>
       <c r="E734" s="5" t="n">
@@ -48323,7 +48323,7 @@
       </c>
       <c r="D735" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E735" s="5" t="n">
@@ -48386,7 +48386,7 @@
       </c>
       <c r="D736" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E736" s="5" t="n">
@@ -48515,7 +48515,7 @@
       </c>
       <c r="D738" s="5" t="inlineStr">
         <is>
-          <t>Dumbbells, Bench</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="E738" s="5" t="n">
@@ -48713,7 +48713,7 @@
       </c>
       <c r="D741" s="5" t="inlineStr">
         <is>
-          <t>Bands</t>
+          <t>Long resistance bands</t>
         </is>
       </c>
       <c r="E741" s="5" t="n">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -1000,7 +1000,8 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -3040,7 +3041,8 @@
           <t>Shoulder: Arm overhead (partial)
 Hip: Leg behind you (partial)
 Wrist: Weight on your hands (partial)
-Knee: Kneel (full)</t>
+Knee: Kneel (full)
+Lower back: Arch your back (hold, no movement)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -3492,7 +3494,8 @@
       <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Push (hold, no movement)
-Wrist: Weight on your hands (partial)</t>
+Wrist: Weight on your hands (partial)
+Lower back: Arch your back (hold, no movement)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3749,7 +3752,8 @@
       <c r="K44" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Push (hold, no movement)
-Hip: Leg out to the side (hold, no movement)</t>
+Hip: Leg out to the side (hold, no movement)
+Lower back: Lean to the side (hold, no movement)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -4210,7 +4214,8 @@
       <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (full)
-Lower back: Arch your back (partial)</t>
+Lower back: Arch your back (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -4276,7 +4281,8 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Lower back: Lift from the floor (full)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -4402,7 +4408,8 @@
       <c r="K54" s="5" t="inlineStr">
         <is>
           <t>Ankle: Tiptoe (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -4589,7 +4596,8 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Knee over toes (full)</t>
+          <t>Ankle: Knee over toes (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -4782,7 +4790,8 @@
       <c r="K60" s="5" t="inlineStr">
         <is>
           <t>Ankle: Balance and uneven ground (full)
-Hip: Stand on one leg (full)</t>
+Hip: Stand on one leg (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -4848,7 +4857,8 @@
         <is>
           <t>Shoulder: Push (full)
 Wrist: Weight on your hands (full)
-Hip: Knee toward chest (full)</t>
+Hip: Knee toward chest (full)
+Knee: Bend the knee deep (partial)</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -13512,7 +13522,8 @@
       <c r="K194" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (hold, no movement)
-Wrist: Grip tight (hold, no movement)</t>
+Wrist: Grip tight (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L194" s="5" t="inlineStr">
@@ -13579,7 +13590,8 @@
         <is>
           <t>Shoulder: Carry weight (hold, no movement)
 Wrist: Grip tight (hold, no movement)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
@@ -17638,7 +17650,8 @@
         <is>
           <t>Hip: Leg behind you (full)
 Hip: Stand on one leg (partial)
-Lower back: Arch your back (partial)</t>
+Lower back: Arch your back (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L257" s="5" t="inlineStr">
@@ -17893,7 +17906,8 @@
       <c r="K261" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg out to the side (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L261" s="5" t="inlineStr">
@@ -17958,7 +17972,8 @@
       <c r="K262" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L262" s="5" t="inlineStr">
@@ -18088,7 +18103,8 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Hip: Stand on one leg (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L264" s="5" t="inlineStr">
@@ -18153,7 +18169,8 @@
       <c r="K265" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (full)
-Lower back: Arch your back (hold, no movement)</t>
+Lower back: Arch your back (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L265" s="5" t="inlineStr">
@@ -18610,7 +18627,8 @@
       <c r="K272" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (partial)
-Hip: Leg across (hold, no movement)</t>
+Hip: Leg across (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
@@ -19122,7 +19140,8 @@
       <c r="K280" s="5" t="inlineStr">
         <is>
           <t>Ankle: Tiptoe (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L280" s="5" t="inlineStr">
@@ -19373,7 +19392,8 @@
       <c r="K284" s="5" t="inlineStr">
         <is>
           <t>Ankle: Knee over toes (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L284" s="5" t="inlineStr">
@@ -19437,7 +19457,8 @@
       <c r="K285" s="5" t="inlineStr">
         <is>
           <t>Ankle: Knee over toes (hold, no movement)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L285" s="5" t="inlineStr">
@@ -19693,7 +19714,8 @@
         <is>
           <t>Lower back: Lean to the side (partial)
 Hip: Knee toward chest (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L289" s="5" t="inlineStr">
@@ -19759,7 +19781,9 @@
         <is>
           <t>Hip: Leg behind you (partial)
 Shoulder: Raise arm in front (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Lower back: Arch your back (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L290" s="5" t="inlineStr">
@@ -19824,7 +19848,8 @@
       <c r="K291" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Push (hold, no movement)
-Wrist: Weight on your hands (hold, no movement)</t>
+Wrist: Weight on your hands (hold, no movement)
+Lower back: Arch your back (hold, no movement)</t>
         </is>
       </c>
       <c r="L291" s="5" t="inlineStr">
@@ -20589,7 +20614,8 @@
         <is>
           <t>Hip: Leg behind you (full)
 Hip: Leg out to the side (hold, no movement)
-Lower back: Arch your back (partial)</t>
+Lower back: Arch your back (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
@@ -20718,7 +20744,8 @@
       <c r="K305" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L305" s="5" t="inlineStr">
@@ -20783,7 +20810,8 @@
       <c r="K306" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (full)
-Lower back: Lift from the floor (partial)</t>
+Lower back: Lift from the floor (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L306" s="5" t="inlineStr">
@@ -21042,7 +21070,8 @@
       <c r="K310" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg across (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L310" s="5" t="inlineStr">
@@ -21240,7 +21269,8 @@
       <c r="K313" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (full)
-Lower back: Arch your back (partial)</t>
+Lower back: Arch your back (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L313" s="5" t="inlineStr">
@@ -21375,7 +21405,8 @@
           <t>Hip: Knee toward chest (full)
 Hip: Stand on one leg (full)
 Ankle: Balance and uneven ground (partial)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L315" s="5" t="inlineStr">
@@ -21503,7 +21534,8 @@
         <is>
           <t>Shoulder: Carry weight (partial)
 Wrist: Grip tight (full)
-Lower back: Lean to the side (hold, no movement)</t>
+Lower back: Lean to the side (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
@@ -21758,7 +21790,8 @@
       </c>
       <c r="K321" s="5" t="inlineStr">
         <is>
-          <t>Hip: Leg out to the side (full)</t>
+          <t>Hip: Leg out to the side (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L321" s="5" t="inlineStr">
@@ -21953,7 +21986,8 @@
       <c r="K324" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (full)
-Lower back: Arch your back (partial)</t>
+Lower back: Arch your back (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L324" s="5" t="inlineStr">
@@ -22019,7 +22053,8 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Hip: Leg behind you (full)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L325" s="5" t="inlineStr">
@@ -22278,7 +22313,8 @@
       <c r="K329" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (full)
-Lower back: Arch your back (partial)</t>
+Lower back: Arch your back (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L329" s="5" t="inlineStr">
@@ -23636,7 +23672,8 @@
           <t>Hip: Knee toward chest (partial)
 Hip: Turn the hip (full)
 Hip: Leg out to the side (partial)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L350" s="5" t="inlineStr">
@@ -23766,7 +23803,8 @@
         <is>
           <t>Ankle: Tiptoe (full)
 Ankle: Knee over toes (partial)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L352" s="5" t="inlineStr">
@@ -23895,7 +23933,8 @@
       </c>
       <c r="K354" s="5" t="inlineStr">
         <is>
-          <t>Hip: Leg out to the side (partial)</t>
+          <t>Hip: Leg out to the side (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L354" s="5" t="inlineStr">
@@ -23961,7 +24000,8 @@
         <is>
           <t>Shoulder: Raise arm to the side (full)
 Shoulder: Arm overhead (partial)
-Hip: Leg out to the side (partial)</t>
+Hip: Leg out to the side (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L355" s="5" t="inlineStr">
@@ -24028,7 +24068,8 @@
         <is>
           <t>Hip: Knee toward chest (partial)
 Shoulder: Raise arm in front (full)
-Shoulder: Arm overhead (partial)</t>
+Shoulder: Arm overhead (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L356" s="5" t="inlineStr">
@@ -24095,7 +24136,8 @@
         <is>
           <t>Hip: Leg out to the side (partial)
 Shoulder: Arm overhead (partial)
-Lower back: Lean to the side (partial)</t>
+Lower back: Lean to the side (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L357" s="5" t="inlineStr">
@@ -24162,7 +24204,8 @@
           <t>Hip: Knee toward chest (full)
 Lower back: Bend forward (partial)
 Wrist: Weight on your hands (full)
-Shoulder: Push (partial)</t>
+Shoulder: Push (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L358" s="5" t="inlineStr">
@@ -24296,7 +24339,8 @@
           <t>Wrist: Weight on your hands (full)
 Shoulder: Reach behind your back (partial)
 Hip: Leg behind you (partial)
-Elbow: Straighten elbow with weight (partial)</t>
+Elbow: Straighten elbow with weight (partial)
+Knee: Bend the knee deep (partial)</t>
         </is>
       </c>
       <c r="L360" s="5" t="inlineStr">
@@ -24429,7 +24473,8 @@
       <c r="K362" s="5" t="inlineStr">
         <is>
           <t>Ankle: Balance and uneven ground (full)
-Hip: Stand on one leg (full)</t>
+Hip: Stand on one leg (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L362" s="5" t="inlineStr">
@@ -24629,7 +24674,8 @@
       </c>
       <c r="K365" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L365" s="5" t="inlineStr">
@@ -27474,7 +27520,8 @@
         <is>
           <t>Ankle: Balance and uneven ground (partial)
 Hip: Stand on one leg (partial)
-Hip: Knee toward chest (hold, no movement)</t>
+Hip: Knee toward chest (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L409" s="5" t="inlineStr">
@@ -27539,7 +27586,8 @@
       <c r="K410" s="5" t="inlineStr">
         <is>
           <t>Ankle: Balance and uneven ground (partial)
-Hip: Leg across (hold, no movement)</t>
+Hip: Leg across (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L410" s="5" t="inlineStr">
@@ -27604,7 +27652,8 @@
       <c r="K411" s="5" t="inlineStr">
         <is>
           <t>Ankle: Balance and uneven ground (full)
-Hip: Stand on one leg (partial)</t>
+Hip: Stand on one leg (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L411" s="5" t="inlineStr">
@@ -27670,7 +27719,8 @@
         <is>
           <t>Hip: Leg out to the side (partial)
 Hip: Stand on one leg (partial)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L412" s="5" t="inlineStr">
@@ -27804,7 +27854,8 @@
 Hip: Stand on one leg (full)
 Hip: Knee toward chest (partial)
 Hip: Leg out to the side (partial)
-Hip: Leg behind you (partial)</t>
+Hip: Leg behind you (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L414" s="5" t="inlineStr">
@@ -27869,7 +27920,8 @@
       <c r="K415" s="5" t="inlineStr">
         <is>
           <t>Ankle: Balance and uneven ground (full)
-Hip: Leg across (hold, no movement)</t>
+Hip: Leg across (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L415" s="5" t="inlineStr">
@@ -27936,7 +27988,8 @@
           <t>Ankle: Balance and uneven ground (full)
 Hip: Stand on one leg (full)
 Hip: Knee toward chest (partial)
-Lower back: Bend forward (partial)</t>
+Lower back: Bend forward (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L416" s="5" t="inlineStr">
@@ -28714,7 +28767,8 @@
         <is>
           <t>Shoulder: Carry weight (hold, no movement)
 Wrist: Grip tight (hold, no movement)
-Lower back: Lean to the side (hold, no movement)</t>
+Lower back: Lean to the side (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L428" s="5" t="inlineStr">
@@ -28780,7 +28834,9 @@
         <is>
           <t>Shoulder: Carry weight (hold, no movement)
 Elbow: Bend elbow with weight (hold, no movement)
-Wrist: Grip tight (hold, no movement)</t>
+Wrist: Grip tight (hold, no movement)
+Lower back: Arch your back (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L429" s="5" t="inlineStr">
@@ -31082,7 +31138,8 @@
       <c r="K465" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (hold, no movement)
-Lower back: Arch your back (hold, no movement)</t>
+Lower back: Arch your back (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L465" s="5" t="inlineStr">
@@ -31406,7 +31463,8 @@
         <is>
           <t>Hip: Leg out to the side (hold, no movement)
 Lower back: Lean to the side (hold, no movement)
-Hip: Stand on one leg (hold, no movement)</t>
+Hip: Stand on one leg (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L470" s="5" t="inlineStr">
@@ -31599,7 +31657,8 @@
         <is>
           <t>Hip: Knee toward chest (hold, no movement)
 Hip: Stand on one leg (hold, no movement)
-Ankle: Balance and uneven ground (hold, no movement)</t>
+Ankle: Balance and uneven ground (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L473" s="5" t="inlineStr">
@@ -31789,7 +31848,8 @@
       <c r="K476" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (hold, no movement)
-Hip: Leg across (hold, no movement)</t>
+Hip: Leg across (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L476" s="5" t="inlineStr">
@@ -31917,7 +31977,8 @@
       </c>
       <c r="K478" s="5" t="inlineStr">
         <is>
-          <t>Hip: Turn the hip (hold, no movement)</t>
+          <t>Hip: Turn the hip (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L478" s="5" t="inlineStr">
@@ -32172,7 +32233,8 @@
       <c r="K482" s="5" t="inlineStr">
         <is>
           <t>Hip: Stand on one leg (hold, no movement)
-Ankle: Balance and uneven ground (hold, no movement)</t>
+Ankle: Balance and uneven ground (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L482" s="5" t="inlineStr">
@@ -33006,7 +33068,8 @@
       </c>
       <c r="K495" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Knee over toes (hold, no movement)</t>
+          <t>Ankle: Knee over toes (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L495" s="5" t="inlineStr">
@@ -33068,7 +33131,8 @@
       </c>
       <c r="K496" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Tiptoe (hold, no movement)</t>
+          <t>Ankle: Tiptoe (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L496" s="5" t="inlineStr">
@@ -33131,7 +33195,8 @@
       </c>
       <c r="K497" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Balance and uneven ground (hold, no movement)</t>
+          <t>Ankle: Balance and uneven ground (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L497" s="5" t="inlineStr">
@@ -33194,7 +33259,8 @@
       </c>
       <c r="K498" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Balance and uneven ground (hold, no movement)</t>
+          <t>Ankle: Balance and uneven ground (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L498" s="5" t="inlineStr">
@@ -33257,7 +33323,8 @@
       <c r="K499" s="5" t="inlineStr">
         <is>
           <t>Ankle: Tiptoe (hold, no movement)
-Ankle: Balance and uneven ground (hold, no movement)</t>
+Ankle: Balance and uneven ground (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L499" s="5" t="inlineStr">
@@ -33381,7 +33448,8 @@
       </c>
       <c r="K501" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Knee over toes (partial)</t>
+          <t>Ankle: Knee over toes (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L501" s="5" t="inlineStr">
@@ -33443,7 +33511,8 @@
       </c>
       <c r="K502" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Tiptoe (partial)</t>
+          <t>Ankle: Tiptoe (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L502" s="5" t="inlineStr">
@@ -33506,7 +33575,8 @@
       <c r="K503" s="5" t="inlineStr">
         <is>
           <t>Ankle: Tiptoe (partial)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L503" s="5" t="inlineStr">
@@ -33944,7 +34014,8 @@
       </c>
       <c r="K510" s="5" t="inlineStr">
         <is>
-          <t>Hip: Leg out to the side (partial)</t>
+          <t>Hip: Leg out to the side (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L510" s="5" t="inlineStr">
@@ -34200,7 +34271,8 @@
       </c>
       <c r="K514" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L514" s="5" t="inlineStr">
@@ -34266,7 +34338,8 @@
         <is>
           <t>Shoulder: Push (partial)
 Elbow: Straighten elbow with weight (partial)
-Lower back: Twist (partial)</t>
+Lower back: Twist (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L515" s="5" t="inlineStr">
@@ -34332,7 +34405,8 @@
         <is>
           <t>Hip: Leg out to the side (partial)
 Shoulder: Raise arm to the side (full)
-Shoulder: Arm overhead (partial)</t>
+Shoulder: Arm overhead (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L516" s="5" t="inlineStr">
@@ -34397,7 +34471,8 @@
       <c r="K517" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg out to the side (partial)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Stairs (partial)</t>
         </is>
       </c>
       <c r="L517" s="5" t="inlineStr">
@@ -38889,7 +38964,8 @@
         <is>
           <t>Hip: Leg across (partial)
 Hip: Stand on one leg (hold, no movement)
-Ankle: Balance and uneven ground (hold, no movement)</t>
+Ankle: Balance and uneven ground (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L587" s="5" t="inlineStr">
@@ -44693,7 +44769,8 @@
         <is>
           <t>Shoulder: Carry weight (partial)
 Wrist: Grip tight (hold, no movement)
-Lower back: Lean to the side (hold, no movement)</t>
+Lower back: Lean to the side (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L678" s="5" t="inlineStr">
@@ -44759,7 +44836,8 @@
         <is>
           <t>Shoulder: Carry weight (partial)
 Wrist: Grip tight (hold, no movement)
-Lower back: Arch your back (hold, no movement)</t>
+Lower back: Arch your back (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L679" s="5" t="inlineStr">
@@ -45330,7 +45408,8 @@
         <is>
           <t>Lower back: Lift from the floor (partial)
 Hip: Leg behind you (partial)
-Wrist: Grip tight (hold, no movement)</t>
+Wrist: Grip tight (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L688" s="5" t="inlineStr">
@@ -45397,7 +45476,8 @@
         <is>
           <t>Lower back: Lift from the floor (partial)
 Hip: Leg behind you (partial)
-Wrist: Grip tight (hold, no movement)</t>
+Wrist: Grip tight (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L689" s="5" t="inlineStr">
@@ -47977,7 +48057,8 @@
         <is>
           <t>Lower back: Lift from the floor (full)
 Hip: Leg behind you (full)
-Wrist: Grip tight (hold, no movement)</t>
+Wrist: Grip tight (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L729" s="5" t="inlineStr">
@@ -48104,7 +48185,8 @@
       <c r="K731" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg out to the side (full)
-Hip: Stand on one leg (hold, no movement)</t>
+Hip: Stand on one leg (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L731" s="5" t="inlineStr">
@@ -48167,7 +48249,8 @@
       <c r="K732" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg across (full)
-Hip: Stand on one leg (hold, no movement)</t>
+Hip: Stand on one leg (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L732" s="5" t="inlineStr">
@@ -48230,7 +48313,8 @@
       <c r="K733" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg across (full)
-Hip: Stand on one leg (hold, no movement)</t>
+Hip: Stand on one leg (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L733" s="5" t="inlineStr">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -24176,7 +24176,7 @@
       </c>
       <c r="F358" s="5" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>13+ (teens)</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -1064,7 +1064,8 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -1458,7 +1459,8 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Hip: Leg behind you (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Twist on the knee (partial)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -2909,7 +2911,8 @@
       <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4472,7 +4475,8 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (full)</t>
+          <t>Hip: Knee toward chest (full)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -5182,7 +5186,8 @@
       <c r="K66" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (full)
-Lower back: Bend forward (partial)</t>
+Lower back: Bend forward (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -5309,7 +5314,8 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Knee over toes (full)</t>
+          <t>Ankle: Knee over toes (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -10773,7 +10779,8 @@
       <c r="K152" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (partial)</t>
+Wrist: Grip tight (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
@@ -12470,7 +12477,8 @@
           <t>Shoulder: Push (full)
 Elbow: Straighten elbow with weight (full)
 Wrist: Grip tight (partial)
-Hip: Leg behind you (hold, no movement)</t>
+Hip: Leg behind you (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
@@ -12538,7 +12546,8 @@
           <t>Shoulder: Push (full)
 Elbow: Straighten elbow with weight (full)
 Wrist: Grip tight (partial)
-Hip: Leg behind you (hold, no movement)</t>
+Hip: Leg behind you (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L179" s="5" t="inlineStr">
@@ -12605,7 +12614,8 @@
           <t>Shoulder: Push (partial)
 Elbow: Straighten elbow with weight (full)
 Wrist: Grip tight (full)
-Hip: Leg behind you (hold, no movement)</t>
+Hip: Leg behind you (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
@@ -16080,7 +16090,8 @@
       <c r="K233" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L233" s="5" t="inlineStr">
@@ -16144,7 +16155,8 @@
       <c r="K234" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L234" s="5" t="inlineStr">
@@ -18677,7 +18689,7 @@
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>Hip, Shoulder, Pregnant / postpartum, Recent surgery</t>
+          <t>Hip, Shoulder, Pregnant / postpartum, Recent surgery, Knee</t>
         </is>
       </c>
       <c r="I273" s="5" t="inlineStr">
@@ -18694,7 +18706,8 @@
         <is>
           <t>Hip: Leg across (hold, no movement)
 Shoulder: Push (hold, no movement)
-Lower back: Lean to the side (hold, no movement)</t>
+Lower back: Lean to the side (hold, no movement)
+Knee: Kneel (hold, no movement)</t>
         </is>
       </c>
       <c r="L273" s="5" t="inlineStr">
@@ -18821,7 +18834,8 @@
       </c>
       <c r="K275" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L275" s="5" t="inlineStr">
@@ -21468,7 +21482,8 @@
       </c>
       <c r="K316" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Tiptoe (full)</t>
+          <t>Ankle: Tiptoe (full)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L316" s="5" t="inlineStr">
@@ -22117,7 +22132,8 @@
       <c r="K326" s="5" t="inlineStr">
         <is>
           <t>Ankle: Tiptoe (full)
-Ankle: Knee over toes (partial)</t>
+Ankle: Knee over toes (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L326" s="5" t="inlineStr">
@@ -22957,7 +22973,8 @@
       </c>
       <c r="K339" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L339" s="5" t="inlineStr">
@@ -23212,7 +23229,8 @@
       </c>
       <c r="K343" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L343" s="5" t="inlineStr">
@@ -23604,7 +23622,8 @@
         <is>
           <t>Hip: Leg out to the side (full)
 Hip: Leg across (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Twist on the knee (partial)</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
@@ -25002,7 +25021,8 @@
       <c r="K370" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Arm overhead (partial)
-Hip: Knee toward chest (partial)</t>
+Hip: Knee toward chest (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L370" s="5" t="inlineStr">
@@ -25969,7 +25989,8 @@
       <c r="K385" s="5" t="inlineStr">
         <is>
           <t>Lower back: Bend forward (full)
-Hip: Knee toward chest (full)</t>
+Hip: Knee toward chest (full)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L385" s="5" t="inlineStr">
@@ -26684,7 +26705,8 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Hip: Stand on one leg (partial)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L396" s="5" t="inlineStr">
@@ -26811,7 +26833,8 @@
       <c r="K398" s="5" t="inlineStr">
         <is>
           <t>Ankle: Knee over toes (full)
-Ankle: Balance and uneven ground (partial)</t>
+Ankle: Balance and uneven ground (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L398" s="5" t="inlineStr">
@@ -27390,7 +27413,8 @@
       </c>
       <c r="K407" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L407" s="5" t="inlineStr">
@@ -31204,7 +31228,8 @@
       <c r="K466" s="5" t="inlineStr">
         <is>
           <t>Lower back: Arch your back (hold, no movement)
-Hip: Leg behind you (hold, no movement)</t>
+Hip: Leg behind you (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L466" s="5" t="inlineStr">
@@ -31721,7 +31746,8 @@
       </c>
       <c r="K474" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (hold, no movement)</t>
+          <t>Hip: Knee toward chest (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L474" s="5" t="inlineStr">
@@ -31897,7 +31923,7 @@
       </c>
       <c r="H477" s="5" t="inlineStr">
         <is>
-          <t>Recent surgery, Pregnant / postpartum</t>
+          <t>Recent surgery, Pregnant / postpartum, Knee</t>
         </is>
       </c>
       <c r="I477" s="5" t="inlineStr">
@@ -31914,7 +31940,8 @@
         <is>
           <t>Hip: Leg across (hold, no movement)
 Shoulder: Push (hold, no movement)
-Lower back: Lean to the side (hold, no movement)</t>
+Lower back: Lean to the side (hold, no movement)
+Knee: Kneel (hold, no movement)</t>
         </is>
       </c>
       <c r="L477" s="5" t="inlineStr">
@@ -34142,7 +34169,8 @@
       </c>
       <c r="K512" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L512" s="5" t="inlineStr">
@@ -34666,7 +34694,8 @@
       </c>
       <c r="K520" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L520" s="5" t="inlineStr">
@@ -35944,7 +35973,8 @@
       </c>
       <c r="K540" s="5" t="inlineStr">
         <is>
-          <t>Hip: Knee toward chest (partial)</t>
+          <t>Hip: Knee toward chest (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L540" s="5" t="inlineStr">
@@ -38708,7 +38738,8 @@
       <c r="K583" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (partial)
-Hip: Turn the hip (partial)</t>
+Hip: Turn the hip (partial)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L583" s="5" t="inlineStr">
@@ -39790,7 +39821,8 @@
       </c>
       <c r="K600" s="5" t="inlineStr">
         <is>
-          <t>Ankle: Tiptoe (full)</t>
+          <t>Ankle: Tiptoe (full)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L600" s="5" t="inlineStr">
@@ -40169,7 +40201,8 @@
       </c>
       <c r="K606" s="5" t="inlineStr">
         <is>
-          <t>Lower back: Arch your back (partial)</t>
+          <t>Lower back: Arch your back (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L606" s="5" t="inlineStr">
@@ -40234,7 +40267,8 @@
       <c r="K607" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (partial)
-Lower back: Arch your back (hold, no movement)</t>
+Lower back: Arch your back (hold, no movement)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L607" s="5" t="inlineStr">
@@ -43361,7 +43395,8 @@
       <c r="K656" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (full)
-Lower back: Bend forward (partial)</t>
+Lower back: Bend forward (partial)
+Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
       <c r="L656" s="5" t="inlineStr">
@@ -44189,7 +44224,8 @@
       <c r="K669" s="5" t="inlineStr">
         <is>
           <t>Hip: Knee toward chest (partial)
-Ankle: Knee over toes (partial)</t>
+Ankle: Knee over toes (partial)
+Knee: Bend the knee deep (partial)</t>
         </is>
       </c>
       <c r="L669" s="5" t="inlineStr">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -3741,7 +3741,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Shoulder, Recent surgery</t>
+          <t>Shoulder, Recent surgery, High blood pressure</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Anchor the band high, kneel or stand, and pull your elbows down to your sides toward your back pockets.</t>
+          <t>Anchor the band high, sit or stand, and pull your elbows down to your sides toward your back pockets.</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>Hip, Shoulder, Pregnant / postpartum, Recent surgery, Knee</t>
+          <t>Hip, Shoulder, Pregnant / postpartum, Recent surgery, Knee, High blood pressure</t>
         </is>
       </c>
       <c r="I274" s="5" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>Shoulder, Recent surgery, Knee</t>
+          <t>Shoulder, Recent surgery, Knee, High blood pressure</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>Lower back, Recent surgery</t>
+          <t>Lower back, Recent surgery, High blood pressure</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
@@ -31038,7 +31038,8 @@
       <c r="K463" s="5" t="inlineStr">
         <is>
           <t>Lower back: Bend forward (hold, no movement)
-Hip: Knee toward chest (hold, no movement)</t>
+Hip: Knee toward chest (hold, no movement)
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L463" s="5" t="inlineStr">
@@ -31478,7 +31479,7 @@
       </c>
       <c r="H470" s="5" t="inlineStr">
         <is>
-          <t>Recent surgery, Shoulder, Knee</t>
+          <t>Recent surgery, Shoulder, Knee, High blood pressure</t>
         </is>
       </c>
       <c r="I470" s="5" t="inlineStr">
@@ -31997,7 +31998,7 @@
       </c>
       <c r="H478" s="5" t="inlineStr">
         <is>
-          <t>Recent surgery, Pregnant / postpartum, Knee</t>
+          <t>Recent surgery, Pregnant / postpartum, Knee, High blood pressure</t>
         </is>
       </c>
       <c r="I478" s="5" t="inlineStr">
@@ -32063,7 +32064,8 @@
       </c>
       <c r="H479" s="5" t="inlineStr">
         <is>
-          <t>Recent surgery</t>
+          <t>Recent surgery
+REVIEWER: clinician decides whether this loads the knee / pivots the knee</t>
         </is>
       </c>
       <c r="I479" s="5" t="inlineStr">
@@ -32127,7 +32129,8 @@
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>Recent surgery</t>
+          <t>Recent surgery
+REVIEWER: clinician decides whether this loads the knee / pivots the knee</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
@@ -47465,7 +47468,8 @@
       <c r="K719" s="5" t="inlineStr">
         <is>
           <t>Lower back: Bend forward (full)
-Hip: Knee toward chest (full)</t>
+Hip: Knee toward chest (full)
+Knee: Bend the knee deep (partial)</t>
         </is>
       </c>
       <c r="L719" s="5" t="inlineStr">
@@ -48550,7 +48554,8 @@
       </c>
       <c r="H736" s="5" t="inlineStr">
         <is>
-          <t>Hip, Recent surgery</t>
+          <t>Hip, Recent surgery
+REVIEWER: clinician decides whether this loads the knee / pivots the knee</t>
         </is>
       </c>
       <c r="I736" s="5" t="inlineStr">
@@ -48613,7 +48618,8 @@
       </c>
       <c r="H737" s="5" t="inlineStr">
         <is>
-          <t>Hip, Recent surgery</t>
+          <t>Hip, Recent surgery
+REVIEWER: clinician decides whether this loads the knee / pivots the knee</t>
         </is>
       </c>
       <c r="I737" s="5" t="inlineStr">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -2911,7 +2911,7 @@
       <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (full)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -3043,7 +3043,7 @@
         <is>
           <t>Shoulder: Arm overhead (partial)
 Hip: Leg behind you (partial)
-Wrist: Weight on your hands (partial)
+Wrist: Weight on your hands (hold, no movement)
 Knee: Kneel (full)
 Lower back: Arch your back (hold, no movement)</t>
         </is>
@@ -3497,7 +3497,7 @@
       <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Push (hold, no movement)
-Wrist: Weight on your hands (partial)
+Wrist: Weight on your hands (hold, no movement)
 Lower back: Arch your back (hold, no movement)</t>
         </is>
       </c>
@@ -3692,7 +3692,7 @@
         <is>
           <t>Lower back: Bend forward (full)
 Hip: Knee toward chest (full)
-Knee: Bend the knee deep (partial)</t>
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3956,7 +3956,7 @@
           <t>Knee: Bend the knee deep (full)
 Hip: Deep squat (full)
 Ankle: Knee over toes (full)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (hold, no movement)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -4219,7 +4219,7 @@
       <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (full)
-Lower back: Arch your back (partial)
+Lower back: Arch your back (hold, no movement)
 Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
@@ -4286,7 +4286,7 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Lower back: Lift from the floor (full)
-Wrist: Grip tight (full)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -10845,7 +10845,7 @@
       <c r="K153" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (partial)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -16156,7 +16156,7 @@
       <c r="K234" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (full)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -16221,7 +16221,7 @@
       <c r="K235" s="5" t="inlineStr">
         <is>
           <t>Shoulder: Carry weight (full)
-Wrist: Grip tight (full)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -17728,7 +17728,7 @@
         <is>
           <t>Hip: Leg behind you (full)
 Hip: Stand on one leg (partial)
-Lower back: Arch your back (partial)
+Lower back: Arch your back (hold, no movement)
 Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
@@ -20696,7 +20696,7 @@
         <is>
           <t>Hip: Leg behind you (full)
 Hip: Leg out to the side (hold, no movement)
-Lower back: Arch your back (partial)
+Lower back: Arch your back (hold, no movement)
 Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
@@ -21221,7 +21221,7 @@
           <t>Knee: Bend the knee deep (full)
 Hip: Leg behind you (partial)
 Ankle: Knee over toes (partial)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (hold, no movement)</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
@@ -21287,7 +21287,7 @@
           <t>Knee: Bend the knee deep (partial)
 Hip: Deep squat (partial)
 Ankle: Knee over toes (partial)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (hold, no movement)</t>
         </is>
       </c>
       <c r="L313" s="5" t="inlineStr">
@@ -21352,7 +21352,7 @@
       <c r="K314" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (full)
-Lower back: Arch your back (partial)
+Lower back: Arch your back (hold, no movement)
 Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
@@ -21420,7 +21420,7 @@
           <t>Knee: Bend the knee deep (full)
 Hip: Deep squat (full)
 Hip: Leg out to the side (partial)
-Wrist: Grip tight (full)</t>
+Wrist: Grip tight (hold, no movement)</t>
         </is>
       </c>
       <c r="L315" s="5" t="inlineStr">
@@ -21488,7 +21488,7 @@
           <t>Hip: Knee toward chest (full)
 Hip: Stand on one leg (full)
 Ankle: Balance and uneven ground (partial)
-Wrist: Grip tight (full)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -21616,8 +21616,8 @@
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>Shoulder: Carry weight (partial)
-Wrist: Grip tight (full)
+          <t>Shoulder: Carry weight (hold, no movement)
+Wrist: Grip tight (hold, no movement)
 Lower back: Lean to the side (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
@@ -21685,7 +21685,7 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Shoulder: Raise arm in front (hold, no movement)
-Wrist: Grip tight (partial)
+Wrist: Grip tight (hold, no movement)
 Knee: Bend the knee deep (partial)</t>
         </is>
       </c>
@@ -22006,7 +22006,7 @@
 Hip: Deep squat (full)
 Ankle: Knee over toes (full)
 Lower back: Lift from the floor (hold, no movement)
-Shoulder: Turn arm outward (partial)</t>
+Shoulder: Turn arm outward (hold, no movement)</t>
         </is>
       </c>
       <c r="L324" s="5" t="inlineStr">
@@ -22071,7 +22071,7 @@
       <c r="K325" s="5" t="inlineStr">
         <is>
           <t>Hip: Leg behind you (full)
-Lower back: Arch your back (partial)
+Lower back: Arch your back (hold, no movement)
 Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
@@ -22138,7 +22138,7 @@
         <is>
           <t>Hip: Knee toward chest (full)
 Hip: Leg behind you (full)
-Wrist: Grip tight (full)
+Wrist: Grip tight (hold, no movement)
 Knee: Straighten with effort (hold, no movement)</t>
         </is>
       </c>
@@ -47469,7 +47469,7 @@
         <is>
           <t>Lower back: Bend forward (full)
 Hip: Knee toward chest (full)
-Knee: Bend the knee deep (partial)</t>
+Knee: Bend the knee deep (hold, no movement)</t>
         </is>
       </c>
       <c r="L719" s="5" t="inlineStr">

--- a/docs/review/exercise-review.xlsx
+++ b/docs/review/exercise-review.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Movements" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$N$755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Exercises'!$A$1:$N$768</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTA(Exercises!$A$2:$A$755)</f>
+        <f>COUNTA(Exercises!$A$2:$A$768)</f>
         <v/>
       </c>
     </row>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>COUNTIF(Exercises!$M$2:$M$755,"Approve")</f>
+        <f>COUNTIF(Exercises!$M$2:$M$768,"Approve")</f>
         <v/>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>COUNTIF(Exercises!$M$2:$M$755,"Fix")</f>
+        <f>COUNTIF(Exercises!$M$2:$M$768,"Fix")</f>
         <v/>
       </c>
     </row>
@@ -856,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N755"/>
+  <dimension ref="A1:N768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -49812,10 +49812,846 @@
       <c r="M755" s="6" t="n"/>
       <c r="N755" s="6" t="n"/>
     </row>
+    <row r="756">
+      <c r="A756" s="5" t="inlineStr">
+        <is>
+          <t>pendulum_swing</t>
+        </is>
+      </c>
+      <c r="B756" s="5" t="inlineStr">
+        <is>
+          <t>Pendulum swing</t>
+        </is>
+      </c>
+      <c r="C756" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.7
+Front shoulders (Deltoid · front head): secondary, 0.5</t>
+        </is>
+      </c>
+      <c r="D756" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E756" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F756" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G756" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support</t>
+        </is>
+      </c>
+      <c r="H756" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I756" s="5" t="inlineStr">
+        <is>
+          <t>Lean forward with one hand on a table and let the other arm hang loose. Move your body so the arm swings gently forward and back, then side to side, then in small circles; switch arms. Keep your back straight and knees slightly bent.</t>
+        </is>
+      </c>
+      <c r="J756" s="5" t="inlineStr">
+        <is>
+          <t>Main work, Warm-up: mobility · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K756" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (partial)
+Shoulder: Raise arm to the side (partial)</t>
+        </is>
+      </c>
+      <c r="L756" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M756" s="6" t="n"/>
+      <c r="N756" s="6" t="n"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="5" t="inlineStr">
+        <is>
+          <t>crossover_arm_stretch</t>
+        </is>
+      </c>
+      <c r="B757" s="5" t="inlineStr">
+        <is>
+          <t>Crossover arm stretch</t>
+        </is>
+      </c>
+      <c r="C757" s="5" t="inlineStr">
+        <is>
+          <t>Rear shoulders (Deltoid · rear head): primary, 0.8
+Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D757" s="5" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="E757" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F757" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G757" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H757" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I757" s="5" t="inlineStr">
+        <is>
+          <t>Relax your shoulders. With the other hand on your arm, just above the elbow, bring the arm across your chest until you feel the stretch at the back of the shoulder. Hold 30 s, release 30 s. Don't pull on the elbow itself.</t>
+        </is>
+      </c>
+      <c r="J757" s="5" t="inlineStr">
+        <is>
+          <t>Main work, Cool-down: stretch · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K757" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front (partial)</t>
+        </is>
+      </c>
+      <c r="L757" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm in front</t>
+        </is>
+      </c>
+      <c r="M757" s="6" t="n"/>
+      <c r="N757" s="6" t="n"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="5" t="inlineStr">
+        <is>
+          <t>stick_internal_rotation_stretch</t>
+        </is>
+      </c>
+      <c r="B758" s="5" t="inlineStr">
+        <is>
+          <t>Stick internal rotation stretch</t>
+        </is>
+      </c>
+      <c r="C758" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Front shoulders (Deltoid · front head): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D758" s="5" t="inlineStr">
+        <is>
+          <t>Light stick (broom handle)</t>
+        </is>
+      </c>
+      <c r="E758" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F758" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G758" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support</t>
+        </is>
+      </c>
+      <c r="H758" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I758" s="5" t="inlineStr">
+        <is>
+          <t>Hold a light stick behind your back at hip height with both hands. With the hand on your good side, pull the stick to the side until you feel a gentle, painless pull in the affected shoulder. Hold 30 s, release 30 s. Don't lean or twist your body.</t>
+        </is>
+      </c>
+      <c r="J758" s="5" t="inlineStr">
+        <is>
+          <t>Main work, Cool-down: stretch · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K758" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward (partial)
+Shoulder: Reach behind your back (partial)</t>
+        </is>
+      </c>
+      <c r="L758" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward</t>
+        </is>
+      </c>
+      <c r="M758" s="6" t="n"/>
+      <c r="N758" s="6" t="n"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="5" t="inlineStr">
+        <is>
+          <t>stick_external_rotation_stretch</t>
+        </is>
+      </c>
+      <c r="B759" s="5" t="inlineStr">
+        <is>
+          <t>Stick external rotation stretch</t>
+        </is>
+      </c>
+      <c r="C759" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Rear shoulders (Deltoid · rear head): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D759" s="5" t="inlineStr">
+        <is>
+          <t>Light stick (broom handle)</t>
+        </is>
+      </c>
+      <c r="E759" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F759" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G759" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H759" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I759" s="5" t="inlineStr">
+        <is>
+          <t>Keep the elbow of the affected side against your body, bent to 90°. Hold one end of a light stick with that hand and the other end with your good hand. Push the stick toward the affected side, turning the forearm out, until you feel a gentle, painless pull. Hold 30 s, release 30 s. Keep your hips facing forward.</t>
+        </is>
+      </c>
+      <c r="J759" s="5" t="inlineStr">
+        <is>
+          <t>Main work, Cool-down: stretch · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K759" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward (partial)</t>
+        </is>
+      </c>
+      <c r="L759" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward</t>
+        </is>
+      </c>
+      <c r="M759" s="6" t="n"/>
+      <c r="N759" s="6" t="n"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="5" t="inlineStr">
+        <is>
+          <t>sleeper_stretch</t>
+        </is>
+      </c>
+      <c r="B760" s="5" t="inlineStr">
+        <is>
+          <t>Sleeper stretch</t>
+        </is>
+      </c>
+      <c r="C760" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Rear shoulders (Deltoid · rear head): secondary, 0.5</t>
+        </is>
+      </c>
+      <c r="D760" s="5" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="E760" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F760" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G760" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H760" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I760" s="5" t="inlineStr">
+        <is>
+          <t>Lie on the affected side with a pillow under your head. Put the bottom arm in front of you, elbow bent to 90° and hand pointing up. With the other hand, slowly push the forearm down toward the floor until you feel the stretch at the back of the shoulder. Hold 30 s, release 30 s. Push on the forearm, never the wrist, and don't bend the wrist.</t>
+        </is>
+      </c>
+      <c r="J760" s="5" t="inlineStr">
+        <is>
+          <t>Main work, Cool-down: stretch · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K760" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward (partial)</t>
+        </is>
+      </c>
+      <c r="L760" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward</t>
+        </is>
+      </c>
+      <c r="M760" s="6" t="n"/>
+      <c r="N760" s="6" t="n"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="5" t="inlineStr">
+        <is>
+          <t>band_external_rotation_90</t>
+        </is>
+      </c>
+      <c r="B761" s="5" t="inlineStr">
+        <is>
+          <t>Band external rotation with the arm at 90°</t>
+        </is>
+      </c>
+      <c r="C761" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Rear shoulders (Deltoid · rear head): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D761" s="5" t="inlineStr">
+        <is>
+          <t>Long resistance bands</t>
+        </is>
+      </c>
+      <c r="E761" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F761" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G761" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support</t>
+        </is>
+      </c>
+      <c r="H761" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I761" s="5" t="inlineStr">
+        <is>
+          <t>Anchor the band in front of you. Lift the arm out to shoulder height, elbow bent to 90° and hand pointing forward. Turn the hand up until it's in line with your head, without dropping the elbow; return slowly. Keep the elbow level with the shoulder.</t>
+        </is>
+      </c>
+      <c r="J761" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K761" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward (partial)
+Shoulder: Raise arm to the side (hold, no movement)
+Wrist: Grip tight (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L761" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward</t>
+        </is>
+      </c>
+      <c r="M761" s="6" t="n"/>
+      <c r="N761" s="6" t="n"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="5" t="inlineStr">
+        <is>
+          <t>band_internal_rotation</t>
+        </is>
+      </c>
+      <c r="B762" s="5" t="inlineStr">
+        <is>
+          <t>Band internal rotation, elbow at your side</t>
+        </is>
+      </c>
+      <c r="C762" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Chest (Pectoralis major): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="D762" s="5" t="inlineStr">
+        <is>
+          <t>Long resistance bands</t>
+        </is>
+      </c>
+      <c r="E762" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G762" s="5" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="H762" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I762" s="5" t="inlineStr">
+        <is>
+          <t>Anchor the band at your side, at elbow height. Keep the elbow against your body, bent to 90°. Bring the hand in across the front of your belly; return slowly. Keep pressing the elbow into your side.</t>
+        </is>
+      </c>
+      <c r="J762" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K762" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L762" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward</t>
+        </is>
+      </c>
+      <c r="M762" s="6" t="n"/>
+      <c r="N762" s="6" t="n"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="5" t="inlineStr">
+        <is>
+          <t>kneeling_thumbs_up_raise</t>
+        </is>
+      </c>
+      <c r="B763" s="5" t="inlineStr">
+        <is>
+          <t>Thumbs-up side raise on a bench</t>
+        </is>
+      </c>
+      <c r="C763" s="5" t="inlineStr">
+        <is>
+          <t>Front shoulders (Deltoid · front head): primary, 0.7
+Rear shoulders (Deltoid · rear head): primary, 0.6
+Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): secondary, 0.5
+Traps (Trapezius): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D763" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbells</t>
+        </is>
+      </c>
+      <c r="E763" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F763" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G763" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H763" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I763" s="5" t="inlineStr">
+        <is>
+          <t>One knee and one hand on a bench or chair, back flat. Let the other arm hang holding a light dumbbell. Raise the arm out to the side to shoulder height, turning the hand until the thumb points up; lower over 5 counts. Pick a weight that makes the last reps hard but never painful.</t>
+        </is>
+      </c>
+      <c r="J763" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K763" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L763" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side</t>
+        </is>
+      </c>
+      <c r="M763" s="6" t="n"/>
+      <c r="N763" s="6" t="n"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="5" t="inlineStr">
+        <is>
+          <t>prone_scapula_setting</t>
+        </is>
+      </c>
+      <c r="B764" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder blade setting, face down</t>
+        </is>
+      </c>
+      <c r="C764" s="5" t="inlineStr">
+        <is>
+          <t>Upper back (Rhomboids and middle trapezius): primary, 0.7
+Traps (Trapezius): secondary, 0.5</t>
+        </is>
+      </c>
+      <c r="D764" s="5" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="E764" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F764" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G764" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H764" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I764" s="5" t="inlineStr">
+        <is>
+          <t>Lie face down with your arms by your sides (a pillow under the forehead if needed). Draw your shoulder blades together and down, ease off halfway and hold 10 s; relax and repeat. Keep your neck relaxed.</t>
+        </is>
+      </c>
+      <c r="J764" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K764" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (hold, no movement)</t>
+        </is>
+      </c>
+      <c r="L764" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M764" s="6" t="n"/>
+      <c r="N764" s="6" t="n"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="5" t="inlineStr">
+        <is>
+          <t>prone_table_scapular_retraction</t>
+        </is>
+      </c>
+      <c r="B765" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder blade squeeze, face down on a bed</t>
+        </is>
+      </c>
+      <c r="C765" s="5" t="inlineStr">
+        <is>
+          <t>Upper back (Rhomboids and middle trapezius): primary, 0.8
+Traps (Trapezius): secondary, 0.5</t>
+        </is>
+      </c>
+      <c r="D765" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbells</t>
+        </is>
+      </c>
+      <c r="E765" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F765" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G765" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H765" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I765" s="5" t="inlineStr">
+        <is>
+          <t>Lie face down on a firm bed or table with the affected arm hanging off the edge, elbow straight. Lift the weight only by squeezing the shoulder blade toward your spine; lower slowly. Don't shrug toward your ear.</t>
+        </is>
+      </c>
+      <c r="J765" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K765" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L765" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Pull</t>
+        </is>
+      </c>
+      <c r="M765" s="6" t="n"/>
+      <c r="N765" s="6" t="n"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="5" t="inlineStr">
+        <is>
+          <t>prone_horizontal_abduction</t>
+        </is>
+      </c>
+      <c r="B766" s="5" t="inlineStr">
+        <is>
+          <t>Face-down side arm raise</t>
+        </is>
+      </c>
+      <c r="C766" s="5" t="inlineStr">
+        <is>
+          <t>Rear shoulders (Deltoid · rear head): primary, 0.8
+Upper back (Rhomboids and middle trapezius): primary, 0.6
+Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): secondary, 0.4</t>
+        </is>
+      </c>
+      <c r="D766" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbells</t>
+        </is>
+      </c>
+      <c r="E766" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F766" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G766" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H766" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I766" s="5" t="inlineStr">
+        <is>
+          <t>Lie face down on a bed or table with the affected arm hanging down. With the arm straight, raise it out to the side to eye level; lower slowly and under control.</t>
+        </is>
+      </c>
+      <c r="J766" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K766" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L766" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Raise arm to the side</t>
+        </is>
+      </c>
+      <c r="M766" s="6" t="n"/>
+      <c r="N766" s="6" t="n"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="5" t="inlineStr">
+        <is>
+          <t>supine_shoulder_rotation_90</t>
+        </is>
+      </c>
+      <c r="B767" s="5" t="inlineStr">
+        <is>
+          <t>Lying shoulder rotation at 90°</t>
+        </is>
+      </c>
+      <c r="C767" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Rear shoulders (Deltoid · rear head): secondary, 0.3
+Chest (Pectoralis major): secondary, 0.2</t>
+        </is>
+      </c>
+      <c r="D767" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbells, Mat</t>
+        </is>
+      </c>
+      <c r="E767" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F767" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G767" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H767" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I767" s="5" t="inlineStr">
+        <is>
+          <t>Lie on your back with the arm out at shoulder height, elbow bent to 90° and fingers pointing up. Keeping the elbow on the floor, turn the forearm forward and back in an arc. If 90° hurts, lower the elbow to 45°. Pick a weight that makes the last reps hard but never painful.</t>
+        </is>
+      </c>
+      <c r="J767" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K767" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward (partial)
+Shoulder: Turn arm inward (partial)
+Shoulder: Raise arm to the side (hold, no movement)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L767" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm outward
+Shoulder: Turn arm inward</t>
+        </is>
+      </c>
+      <c r="M767" s="6" t="n"/>
+      <c r="N767" s="6" t="n"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="5" t="inlineStr">
+        <is>
+          <t>side_lying_internal_rotation</t>
+        </is>
+      </c>
+      <c r="B768" s="5" t="inlineStr">
+        <is>
+          <t>Side-lying internal rotation</t>
+        </is>
+      </c>
+      <c r="C768" s="5" t="inlineStr">
+        <is>
+          <t>Rotator cuff (Supraspinatus, infraspinatus, teres minor, subscapularis): primary, 0.8
+Chest (Pectoralis major): secondary, 0.2</t>
+        </is>
+      </c>
+      <c r="D768" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbells, Mat</t>
+        </is>
+      </c>
+      <c r="E768" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F768" s="5" t="inlineStr">
+        <is>
+          <t>13+ (teens)</t>
+        </is>
+      </c>
+      <c r="G768" s="5" t="inlineStr">
+        <is>
+          <t>With support, Standing</t>
+        </is>
+      </c>
+      <c r="H768" s="5" t="inlineStr">
+        <is>
+          <t>Recent surgery</t>
+        </is>
+      </c>
+      <c r="I768" s="5" t="inlineStr">
+        <is>
+          <t>Lie on the affected side with a pillow or folded towel under your head. Keep the bottom elbow by your side, bent to 90°. Turn the forearm up toward your belly until it's vertical; lower slowly. Don't let your body roll back.</t>
+        </is>
+      </c>
+      <c r="J768" s="5" t="inlineStr">
+        <is>
+          <t>Main work · recovery plan only</t>
+        </is>
+      </c>
+      <c r="K768" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward (partial)
+Wrist: Grip tight (partial)</t>
+        </is>
+      </c>
+      <c r="L768" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder: Turn arm inward</t>
+        </is>
+      </c>
+      <c r="M768" s="6" t="n"/>
+      <c r="N768" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N755"/>
+  <autoFilter ref="A1:N768"/>
   <dataValidations count="1">
-    <dataValidation sqref="M2:M755" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
+    <dataValidation sqref="M2:M768" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve or Fix." prompt="Approve, or Fix and explain in Comment." type="list">
       <formula1>"Approve,Fix"</formula1>
     </dataValidation>
   </dataValidations>
